--- a/src/service_ia/dataset/analyze_none_id.xlsx
+++ b/src/service_ia/dataset/analyze_none_id.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3406"/>
+  <dimension ref="A1:G3401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81919,7 +81919,7 @@
     <row r="3161">
       <c r="A3161" t="inlineStr">
         <is>
-          <t>596ca1a1d730a08971bee6bce1d202aa</t>
+          <t>5923afce4a253b6291278c28d5c3aadd</t>
         </is>
       </c>
       <c r="B3161" s="2" t="n">
@@ -81927,24 +81927,24 @@
       </c>
       <c r="C3161" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Molde FK</t>
         </is>
       </c>
       <c r="D3161" t="inlineStr">
         <is>
-          <t>Vitória SC</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="E3161" t="inlineStr"/>
       <c r="F3161" t="inlineStr"/>
       <c r="G3161" t="n">
-        <v>11098</v>
+        <v>11097</v>
       </c>
     </row>
     <row r="3162">
       <c r="A3162" t="inlineStr">
         <is>
-          <t>5923afce4a253b6291278c28d5c3aadd</t>
+          <t>0cf4782c7b985fbcd8a1861d1cc5ee14</t>
         </is>
       </c>
       <c r="B3162" s="2" t="n">
@@ -81952,49 +81952,49 @@
       </c>
       <c r="C3162" t="inlineStr">
         <is>
-          <t>Molde FK</t>
+          <t>Panathinaikos FC</t>
         </is>
       </c>
       <c r="D3162" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="E3162" t="inlineStr"/>
       <c r="F3162" t="inlineStr"/>
       <c r="G3162" t="n">
-        <v>11097</v>
+        <v>11096</v>
       </c>
     </row>
     <row r="3163">
       <c r="A3163" t="inlineStr">
         <is>
-          <t>0cf4782c7b985fbcd8a1861d1cc5ee14</t>
+          <t>bb17591e16a9194b1356d502ed9d8f6c</t>
         </is>
       </c>
       <c r="B3163" s="2" t="n">
-        <v>45722.73958333334</v>
+        <v>45722.83333333334</v>
       </c>
       <c r="C3163" t="inlineStr">
         <is>
-          <t>Panathinaikos FC</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="D3163" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>FC Lugano</t>
         </is>
       </c>
       <c r="E3163" t="inlineStr"/>
       <c r="F3163" t="inlineStr"/>
       <c r="G3163" t="n">
-        <v>11096</v>
+        <v>11101</v>
       </c>
     </row>
     <row r="3164">
       <c r="A3164" t="inlineStr">
         <is>
-          <t>bb17591e16a9194b1356d502ed9d8f6c</t>
+          <t>d1aad58abd1bd64bdaac43c92fcb4985</t>
         </is>
       </c>
       <c r="B3164" s="2" t="n">
@@ -82002,24 +82002,24 @@
       </c>
       <c r="C3164" t="inlineStr">
         <is>
-          <t>NK Celje</t>
+          <t>Bodø/Glimt</t>
         </is>
       </c>
       <c r="D3164" t="inlineStr">
         <is>
-          <t>FC Lugano</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="E3164" t="inlineStr"/>
       <c r="F3164" t="inlineStr"/>
       <c r="G3164" t="n">
-        <v>11101</v>
+        <v>10804</v>
       </c>
     </row>
     <row r="3165">
       <c r="A3165" t="inlineStr">
         <is>
-          <t>d1aad58abd1bd64bdaac43c92fcb4985</t>
+          <t>4a8205eaadbaa94635b33d44b524ba28</t>
         </is>
       </c>
       <c r="B3165" s="2" t="n">
@@ -82027,24 +82027,24 @@
       </c>
       <c r="C3165" t="inlineStr">
         <is>
-          <t>Bodø/Glimt</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D3165" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="E3165" t="inlineStr"/>
       <c r="F3165" t="inlineStr"/>
       <c r="G3165" t="n">
-        <v>10804</v>
+        <v>10802</v>
       </c>
     </row>
     <row r="3166">
       <c r="A3166" t="inlineStr">
         <is>
-          <t>4a8205eaadbaa94635b33d44b524ba28</t>
+          <t>1541c7d1b031a6005377868264245f95</t>
         </is>
       </c>
       <c r="B3166" s="2" t="n">
@@ -82052,24 +82052,24 @@
       </c>
       <c r="C3166" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="D3166" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>SS Lazio</t>
         </is>
       </c>
       <c r="E3166" t="inlineStr"/>
       <c r="F3166" t="inlineStr"/>
       <c r="G3166" t="n">
-        <v>10802</v>
+        <v>10805</v>
       </c>
     </row>
     <row r="3167">
       <c r="A3167" t="inlineStr">
         <is>
-          <t>1541c7d1b031a6005377868264245f95</t>
+          <t>aa404af4849b159cdc9b40fdbac2dd2b</t>
         </is>
       </c>
       <c r="B3167" s="2" t="n">
@@ -82077,24 +82077,24 @@
       </c>
       <c r="C3167" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="D3167" t="inlineStr">
         <is>
-          <t>SS Lazio</t>
+          <t>Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="E3167" t="inlineStr"/>
       <c r="F3167" t="inlineStr"/>
       <c r="G3167" t="n">
-        <v>10805</v>
+        <v>11099</v>
       </c>
     </row>
     <row r="3168">
       <c r="A3168" t="inlineStr">
         <is>
-          <t>aa404af4849b159cdc9b40fdbac2dd2b</t>
+          <t>eb6c5ff598f5f8d99eab24265a7a3b64</t>
         </is>
       </c>
       <c r="B3168" s="2" t="n">
@@ -82102,24 +82102,24 @@
       </c>
       <c r="C3168" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="D3168" t="inlineStr">
         <is>
-          <t>Cercle Brugge KSV</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="E3168" t="inlineStr"/>
       <c r="F3168" t="inlineStr"/>
       <c r="G3168" t="n">
-        <v>11099</v>
+        <v>11100</v>
       </c>
     </row>
     <row r="3169">
       <c r="A3169" t="inlineStr">
         <is>
-          <t>eb6c5ff598f5f8d99eab24265a7a3b64</t>
+          <t>0139573bd6b8d52cab5313c6c2f940b8</t>
         </is>
       </c>
       <c r="B3169" s="2" t="n">
@@ -82127,249 +82127,249 @@
       </c>
       <c r="C3169" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>FK Borac Banja Luka</t>
         </is>
       </c>
       <c r="D3169" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="E3169" t="inlineStr"/>
       <c r="F3169" t="inlineStr"/>
       <c r="G3169" t="n">
-        <v>11100</v>
+        <v>11102</v>
       </c>
     </row>
     <row r="3170">
       <c r="A3170" t="inlineStr">
         <is>
-          <t>0139573bd6b8d52cab5313c6c2f940b8</t>
+          <t>8dea1f275695d2d017aab64db375a5d8</t>
         </is>
       </c>
       <c r="B3170" s="2" t="n">
-        <v>45722.83333333334</v>
+        <v>45723.79166666666</v>
       </c>
       <c r="C3170" t="inlineStr">
         <is>
-          <t>FK Borac Banja Luka</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="D3170" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="E3170" t="inlineStr"/>
       <c r="F3170" t="inlineStr"/>
       <c r="G3170" t="n">
-        <v>11102</v>
+        <v>13686</v>
       </c>
     </row>
     <row r="3171">
       <c r="A3171" t="inlineStr">
         <is>
-          <t>8dea1f275695d2d017aab64db375a5d8</t>
+          <t>87a4ac8eda5a702239c7b5bea8d471af</t>
         </is>
       </c>
       <c r="B3171" s="2" t="n">
-        <v>45723.79166666666</v>
+        <v>45723.82291666666</v>
       </c>
       <c r="C3171" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="D3171" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>AS Monaco</t>
         </is>
       </c>
       <c r="E3171" t="inlineStr"/>
       <c r="F3171" t="inlineStr"/>
       <c r="G3171" t="n">
-        <v>13686</v>
+        <v>10022</v>
       </c>
     </row>
     <row r="3172">
       <c r="A3172" t="inlineStr">
         <is>
-          <t>87a4ac8eda5a702239c7b5bea8d471af</t>
+          <t>55108bdfab43e8a29e8b42ed67f2fc93</t>
         </is>
       </c>
       <c r="B3172" s="2" t="n">
-        <v>45723.82291666666</v>
+        <v>45724.64583333334</v>
       </c>
       <c r="C3172" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="D3172" t="inlineStr">
         <is>
-          <t>AS Monaco</t>
+          <t>Heracles Almelo</t>
         </is>
       </c>
       <c r="E3172" t="inlineStr"/>
       <c r="F3172" t="inlineStr"/>
       <c r="G3172" t="n">
-        <v>10022</v>
+        <v>13687</v>
       </c>
     </row>
     <row r="3173">
       <c r="A3173" t="inlineStr">
         <is>
-          <t>55108bdfab43e8a29e8b42ed67f2fc93</t>
+          <t>473b0486bd312000b48f531c6e7b2502</t>
         </is>
       </c>
       <c r="B3173" s="2" t="n">
-        <v>45724.64583333334</v>
+        <v>45724.66666666666</v>
       </c>
       <c r="C3173" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="D3173" t="inlineStr">
         <is>
-          <t>Heracles Almelo</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="E3173" t="inlineStr"/>
       <c r="F3173" t="inlineStr"/>
       <c r="G3173" t="n">
-        <v>13687</v>
+        <v>10023</v>
       </c>
     </row>
     <row r="3174">
       <c r="A3174" t="inlineStr">
         <is>
-          <t>473b0486bd312000b48f531c6e7b2502</t>
+          <t>d155a30e07e1ad90d8d05c21340a00eb</t>
         </is>
       </c>
       <c r="B3174" s="2" t="n">
-        <v>45724.66666666666</v>
+        <v>45724.75</v>
       </c>
       <c r="C3174" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="D3174" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="E3174" t="inlineStr"/>
       <c r="F3174" t="inlineStr"/>
       <c r="G3174" t="n">
-        <v>10023</v>
+        <v>10024</v>
       </c>
     </row>
     <row r="3175">
       <c r="A3175" t="inlineStr">
         <is>
-          <t>d155a30e07e1ad90d8d05c21340a00eb</t>
+          <t>6d5f486a4e5bdce2d35fd97955ccf8cb</t>
         </is>
       </c>
       <c r="B3175" s="2" t="n">
-        <v>45724.75</v>
+        <v>45724.79166666666</v>
       </c>
       <c r="C3175" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="D3175" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="E3175" t="inlineStr"/>
       <c r="F3175" t="inlineStr"/>
       <c r="G3175" t="n">
-        <v>10024</v>
+        <v>13688</v>
       </c>
     </row>
     <row r="3176">
       <c r="A3176" t="inlineStr">
         <is>
-          <t>6d5f486a4e5bdce2d35fd97955ccf8cb</t>
+          <t>5b66840b3c25ad102d4c1812dde42c54</t>
         </is>
       </c>
       <c r="B3176" s="2" t="n">
-        <v>45724.79166666666</v>
+        <v>45724.83680555555</v>
       </c>
       <c r="C3176" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="D3176" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>RC Lens</t>
         </is>
       </c>
       <c r="E3176" t="inlineStr"/>
       <c r="F3176" t="inlineStr"/>
       <c r="G3176" t="n">
-        <v>13688</v>
+        <v>10025</v>
       </c>
     </row>
     <row r="3177">
       <c r="A3177" t="inlineStr">
         <is>
-          <t>5b66840b3c25ad102d4c1812dde42c54</t>
+          <t>d3079dde1d6f1961ec66419307a4f4d8</t>
         </is>
       </c>
       <c r="B3177" s="2" t="n">
-        <v>45724.83680555555</v>
+        <v>45725.46875</v>
       </c>
       <c r="C3177" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="D3177" t="inlineStr">
         <is>
-          <t>RC Lens</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="E3177" t="inlineStr"/>
       <c r="F3177" t="inlineStr"/>
       <c r="G3177" t="n">
-        <v>10025</v>
+        <v>13689</v>
       </c>
     </row>
     <row r="3178">
       <c r="A3178" t="inlineStr">
         <is>
-          <t>d3079dde1d6f1961ec66419307a4f4d8</t>
+          <t>d1caef13fa45f271312728e9df8a8270</t>
         </is>
       </c>
       <c r="B3178" s="2" t="n">
-        <v>45725.46875</v>
+        <v>45725.5625</v>
       </c>
       <c r="C3178" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>FC Zwolle</t>
         </is>
       </c>
       <c r="D3178" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="E3178" t="inlineStr"/>
       <c r="F3178" t="inlineStr"/>
       <c r="G3178" t="n">
-        <v>13689</v>
+        <v>13690</v>
       </c>
     </row>
     <row r="3179">
       <c r="A3179" t="inlineStr">
         <is>
-          <t>d1caef13fa45f271312728e9df8a8270</t>
+          <t>818db99cf35d98c5805251b1e72db70a</t>
         </is>
       </c>
       <c r="B3179" s="2" t="n">
@@ -82377,99 +82377,99 @@
       </c>
       <c r="C3179" t="inlineStr">
         <is>
-          <t>FC Zwolle</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="D3179" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="E3179" t="inlineStr"/>
       <c r="F3179" t="inlineStr"/>
       <c r="G3179" t="n">
-        <v>13690</v>
+        <v>13691</v>
       </c>
     </row>
     <row r="3180">
       <c r="A3180" t="inlineStr">
         <is>
-          <t>818db99cf35d98c5805251b1e72db70a</t>
+          <t>25cdb64bead10ef14966ef043264fc05</t>
         </is>
       </c>
       <c r="B3180" s="2" t="n">
-        <v>45725.5625</v>
+        <v>45725.58333333334</v>
       </c>
       <c r="C3180" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="D3180" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="E3180" t="inlineStr"/>
       <c r="F3180" t="inlineStr"/>
       <c r="G3180" t="n">
-        <v>13691</v>
+        <v>10026</v>
       </c>
     </row>
     <row r="3181">
       <c r="A3181" t="inlineStr">
         <is>
-          <t>25cdb64bead10ef14966ef043264fc05</t>
+          <t>1cec5969beb74e501c3df9a72b16db4a</t>
         </is>
       </c>
       <c r="B3181" s="2" t="n">
-        <v>45725.58333333334</v>
+        <v>45725.65625</v>
       </c>
       <c r="C3181" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>FC Twente Enschede</t>
         </is>
       </c>
       <c r="D3181" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="E3181" t="inlineStr"/>
       <c r="F3181" t="inlineStr"/>
       <c r="G3181" t="n">
-        <v>10026</v>
+        <v>13692</v>
       </c>
     </row>
     <row r="3182">
       <c r="A3182" t="inlineStr">
         <is>
-          <t>1cec5969beb74e501c3df9a72b16db4a</t>
+          <t>6fef63685d11976c93142abec63c5cb3</t>
         </is>
       </c>
       <c r="B3182" s="2" t="n">
-        <v>45725.65625</v>
+        <v>45725.67708333334</v>
       </c>
       <c r="C3182" t="inlineStr">
         <is>
-          <t>FC Twente Enschede</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="D3182" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="E3182" t="inlineStr"/>
       <c r="F3182" t="inlineStr"/>
       <c r="G3182" t="n">
-        <v>13692</v>
+        <v>10029</v>
       </c>
     </row>
     <row r="3183">
       <c r="A3183" t="inlineStr">
         <is>
-          <t>6fef63685d11976c93142abec63c5cb3</t>
+          <t>384f8ada97a36033ada2fdb12f838d62</t>
         </is>
       </c>
       <c r="B3183" s="2" t="n">
@@ -82477,24 +82477,24 @@
       </c>
       <c r="C3183" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="D3183" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Saint Etienne</t>
         </is>
       </c>
       <c r="E3183" t="inlineStr"/>
       <c r="F3183" t="inlineStr"/>
       <c r="G3183" t="n">
-        <v>10029</v>
+        <v>10028</v>
       </c>
     </row>
     <row r="3184">
       <c r="A3184" t="inlineStr">
         <is>
-          <t>384f8ada97a36033ada2fdb12f838d62</t>
+          <t>19fa9450c3d273633776055b96852d2e</t>
         </is>
       </c>
       <c r="B3184" s="2" t="n">
@@ -82502,74 +82502,74 @@
       </c>
       <c r="C3184" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Stade de Reims</t>
         </is>
       </c>
       <c r="D3184" t="inlineStr">
         <is>
-          <t>Saint Etienne</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="E3184" t="inlineStr"/>
       <c r="F3184" t="inlineStr"/>
       <c r="G3184" t="n">
-        <v>10028</v>
+        <v>10027</v>
       </c>
     </row>
     <row r="3185">
       <c r="A3185" t="inlineStr">
         <is>
-          <t>19fa9450c3d273633776055b96852d2e</t>
+          <t>6e499b5f373b30ae3f47454d2d273746</t>
         </is>
       </c>
       <c r="B3185" s="2" t="n">
-        <v>45725.67708333334</v>
+        <v>45725.82291666666</v>
       </c>
       <c r="C3185" t="inlineStr">
         <is>
-          <t>Stade de Reims</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="D3185" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E3185" t="inlineStr"/>
       <c r="F3185" t="inlineStr"/>
       <c r="G3185" t="n">
-        <v>10027</v>
+        <v>10030</v>
       </c>
     </row>
     <row r="3186">
       <c r="A3186" t="inlineStr">
         <is>
-          <t>6e499b5f373b30ae3f47454d2d273746</t>
+          <t>6d9903191be7642e9bab46b33aadbc2a</t>
         </is>
       </c>
       <c r="B3186" s="2" t="n">
-        <v>45725.82291666666</v>
+        <v>45729.73958333334</v>
       </c>
       <c r="C3186" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="D3186" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Pafos FC</t>
         </is>
       </c>
       <c r="E3186" t="inlineStr"/>
       <c r="F3186" t="inlineStr"/>
       <c r="G3186" t="n">
-        <v>10030</v>
+        <v>11104</v>
       </c>
     </row>
     <row r="3187">
       <c r="A3187" t="inlineStr">
         <is>
-          <t>6d9903191be7642e9bab46b33aadbc2a</t>
+          <t>e5892ace512504cdf401c1c864062a15</t>
         </is>
       </c>
       <c r="B3187" s="2" t="n">
@@ -82577,24 +82577,24 @@
       </c>
       <c r="C3187" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="D3187" t="inlineStr">
         <is>
-          <t>Pafos FC</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="E3187" t="inlineStr"/>
       <c r="F3187" t="inlineStr"/>
       <c r="G3187" t="n">
-        <v>11104</v>
+        <v>11103</v>
       </c>
     </row>
     <row r="3188">
       <c r="A3188" t="inlineStr">
         <is>
-          <t>e5892ace512504cdf401c1c864062a15</t>
+          <t>95be5e84e10b90df8e3a0f8badc7c81b</t>
         </is>
       </c>
       <c r="B3188" s="2" t="n">
@@ -82602,24 +82602,24 @@
       </c>
       <c r="C3188" t="inlineStr">
         <is>
-          <t>Cercle Brugge KSV</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="D3188" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Bodø/Glimt</t>
         </is>
       </c>
       <c r="E3188" t="inlineStr"/>
       <c r="F3188" t="inlineStr"/>
       <c r="G3188" t="n">
-        <v>11103</v>
+        <v>10808</v>
       </c>
     </row>
     <row r="3189">
       <c r="A3189" t="inlineStr">
         <is>
-          <t>95be5e84e10b90df8e3a0f8badc7c81b</t>
+          <t>096317c4bc002b0cadab57e79744e4ba</t>
         </is>
       </c>
       <c r="B3189" s="2" t="n">
@@ -82627,24 +82627,24 @@
       </c>
       <c r="C3189" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="D3189" t="inlineStr">
         <is>
-          <t>Bodø/Glimt</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="E3189" t="inlineStr"/>
       <c r="F3189" t="inlineStr"/>
       <c r="G3189" t="n">
-        <v>10808</v>
+        <v>10806</v>
       </c>
     </row>
     <row r="3190">
       <c r="A3190" t="inlineStr">
         <is>
-          <t>096317c4bc002b0cadab57e79744e4ba</t>
+          <t>62260cfa07fe1d87e43b5a28e923dc36</t>
         </is>
       </c>
       <c r="B3190" s="2" t="n">
@@ -82652,24 +82652,24 @@
       </c>
       <c r="C3190" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>FC Lugano</t>
         </is>
       </c>
       <c r="D3190" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="E3190" t="inlineStr"/>
       <c r="F3190" t="inlineStr"/>
       <c r="G3190" t="n">
-        <v>10806</v>
+        <v>11105</v>
       </c>
     </row>
     <row r="3191">
       <c r="A3191" t="inlineStr">
         <is>
-          <t>62260cfa07fe1d87e43b5a28e923dc36</t>
+          <t>ef7860bdb3e34e8a2f1fb564533f916b</t>
         </is>
       </c>
       <c r="B3191" s="2" t="n">
@@ -82677,24 +82677,24 @@
       </c>
       <c r="C3191" t="inlineStr">
         <is>
-          <t>FC Lugano</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="D3191" t="inlineStr">
         <is>
-          <t>NK Celje</t>
+          <t>FK Borac Banja Luka</t>
         </is>
       </c>
       <c r="E3191" t="inlineStr"/>
       <c r="F3191" t="inlineStr"/>
       <c r="G3191" t="n">
-        <v>11105</v>
+        <v>11106</v>
       </c>
     </row>
     <row r="3192">
       <c r="A3192" t="inlineStr">
         <is>
-          <t>ef7860bdb3e34e8a2f1fb564533f916b</t>
+          <t>8b3b0adf86162b5f317119d033153aca</t>
         </is>
       </c>
       <c r="B3192" s="2" t="n">
@@ -82702,49 +82702,49 @@
       </c>
       <c r="C3192" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>SS Lazio</t>
         </is>
       </c>
       <c r="D3192" t="inlineStr">
         <is>
-          <t>FK Borac Banja Luka</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="E3192" t="inlineStr"/>
       <c r="F3192" t="inlineStr"/>
       <c r="G3192" t="n">
-        <v>11106</v>
+        <v>10809</v>
       </c>
     </row>
     <row r="3193">
       <c r="A3193" t="inlineStr">
         <is>
-          <t>8b3b0adf86162b5f317119d033153aca</t>
+          <t>9fec965dd19053feb2a5ee473c0d01c0</t>
         </is>
       </c>
       <c r="B3193" s="2" t="n">
-        <v>45729.73958333334</v>
+        <v>45729.83333333334</v>
       </c>
       <c r="C3193" t="inlineStr">
         <is>
-          <t>SS Lazio</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="D3193" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="E3193" t="inlineStr"/>
       <c r="F3193" t="inlineStr"/>
       <c r="G3193" t="n">
-        <v>10809</v>
+        <v>10811</v>
       </c>
     </row>
     <row r="3194">
       <c r="A3194" t="inlineStr">
         <is>
-          <t>9fec965dd19053feb2a5ee473c0d01c0</t>
+          <t>a0e9845e23dbb912ca8c0d8348c849b4</t>
         </is>
       </c>
       <c r="B3194" s="2" t="n">
@@ -82752,24 +82752,24 @@
       </c>
       <c r="C3194" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="D3194" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Molde FK</t>
         </is>
       </c>
       <c r="E3194" t="inlineStr"/>
       <c r="F3194" t="inlineStr"/>
       <c r="G3194" t="n">
-        <v>10811</v>
+        <v>11109</v>
       </c>
     </row>
     <row r="3195">
       <c r="A3195" t="inlineStr">
         <is>
-          <t>b573af9b45f6f88c83d2f7a3ca3648be</t>
+          <t>d2359732baa9a8402c7af0fbbc92f557</t>
         </is>
       </c>
       <c r="B3195" s="2" t="n">
@@ -82777,24 +82777,24 @@
       </c>
       <c r="C3195" t="inlineStr">
         <is>
-          <t>Vitória SC</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D3195" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Panathinaikos FC</t>
         </is>
       </c>
       <c r="E3195" t="inlineStr"/>
       <c r="F3195" t="inlineStr"/>
       <c r="G3195" t="n">
-        <v>11110</v>
+        <v>11108</v>
       </c>
     </row>
     <row r="3196">
       <c r="A3196" t="inlineStr">
         <is>
-          <t>a0e9845e23dbb912ca8c0d8348c849b4</t>
+          <t>f8bff451287e35641a11fc7f77243f7b</t>
         </is>
       </c>
       <c r="B3196" s="2" t="n">
@@ -82802,424 +82802,424 @@
       </c>
       <c r="C3196" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="D3196" t="inlineStr">
         <is>
-          <t>Molde FK</t>
+          <t>FC Copenhagen</t>
         </is>
       </c>
       <c r="E3196" t="inlineStr"/>
       <c r="F3196" t="inlineStr"/>
       <c r="G3196" t="n">
-        <v>11109</v>
+        <v>11107</v>
       </c>
     </row>
     <row r="3197">
       <c r="A3197" t="inlineStr">
         <is>
-          <t>d2359732baa9a8402c7af0fbbc92f557</t>
+          <t>f16009ae54b66ec4b7546825bc8b0c8b</t>
         </is>
       </c>
       <c r="B3197" s="2" t="n">
-        <v>45729.83333333334</v>
+        <v>45730.79166666666</v>
       </c>
       <c r="C3197" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="D3197" t="inlineStr">
         <is>
-          <t>Panathinaikos FC</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="E3197" t="inlineStr"/>
       <c r="F3197" t="inlineStr"/>
       <c r="G3197" t="n">
-        <v>11108</v>
+        <v>13693</v>
       </c>
     </row>
     <row r="3198">
       <c r="A3198" t="inlineStr">
         <is>
-          <t>f8bff451287e35641a11fc7f77243f7b</t>
+          <t>ecc600c5167d6c116aaa433ea74d7bec</t>
         </is>
       </c>
       <c r="B3198" s="2" t="n">
-        <v>45729.83333333334</v>
+        <v>45730.82291666666</v>
       </c>
       <c r="C3198" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="D3198" t="inlineStr">
         <is>
-          <t>FC Copenhagen</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="E3198" t="inlineStr"/>
       <c r="F3198" t="inlineStr"/>
       <c r="G3198" t="n">
-        <v>11107</v>
+        <v>10031</v>
       </c>
     </row>
     <row r="3199">
       <c r="A3199" t="inlineStr">
         <is>
-          <t>f16009ae54b66ec4b7546825bc8b0c8b</t>
+          <t>35dcea1ec2cdbe20987b069ff83709de</t>
         </is>
       </c>
       <c r="B3199" s="2" t="n">
-        <v>45730.79166666666</v>
+        <v>45731.64583333334</v>
       </c>
       <c r="C3199" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="D3199" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="E3199" t="inlineStr"/>
       <c r="F3199" t="inlineStr"/>
       <c r="G3199" t="n">
-        <v>13693</v>
+        <v>13694</v>
       </c>
     </row>
     <row r="3200">
       <c r="A3200" t="inlineStr">
         <is>
-          <t>ecc600c5167d6c116aaa433ea74d7bec</t>
+          <t>23860a2ae8861bf757d11311829e7338</t>
         </is>
       </c>
       <c r="B3200" s="2" t="n">
-        <v>45730.82291666666</v>
+        <v>45731.66666666666</v>
       </c>
       <c r="C3200" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="D3200" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="E3200" t="inlineStr"/>
       <c r="F3200" t="inlineStr"/>
       <c r="G3200" t="n">
-        <v>10031</v>
+        <v>10032</v>
       </c>
     </row>
     <row r="3201">
       <c r="A3201" t="inlineStr">
         <is>
-          <t>35dcea1ec2cdbe20987b069ff83709de</t>
+          <t>1df1a318e1dd7062df128af42a0faa57</t>
         </is>
       </c>
       <c r="B3201" s="2" t="n">
-        <v>45731.64583333334</v>
+        <v>45731.73958333334</v>
       </c>
       <c r="C3201" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="D3201" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>FC Zwolle</t>
         </is>
       </c>
       <c r="E3201" t="inlineStr"/>
       <c r="F3201" t="inlineStr"/>
       <c r="G3201" t="n">
-        <v>13694</v>
+        <v>13695</v>
       </c>
     </row>
     <row r="3202">
       <c r="A3202" t="inlineStr">
         <is>
-          <t>23860a2ae8861bf757d11311829e7338</t>
+          <t>b97ba1c169985ba2f8043d67457868e2</t>
         </is>
       </c>
       <c r="B3202" s="2" t="n">
-        <v>45731.66666666666</v>
+        <v>45731.75</v>
       </c>
       <c r="C3202" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="D3202" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>AS Monaco</t>
         </is>
       </c>
       <c r="E3202" t="inlineStr"/>
       <c r="F3202" t="inlineStr"/>
       <c r="G3202" t="n">
-        <v>10032</v>
+        <v>10033</v>
       </c>
     </row>
     <row r="3203">
       <c r="A3203" t="inlineStr">
         <is>
-          <t>1df1a318e1dd7062df128af42a0faa57</t>
+          <t>72bbd90e1c1cf42d6eb408c43256bf3a</t>
         </is>
       </c>
       <c r="B3203" s="2" t="n">
-        <v>45731.73958333334</v>
+        <v>45731.79166666666</v>
       </c>
       <c r="C3203" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="D3203" t="inlineStr">
         <is>
-          <t>FC Zwolle</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="E3203" t="inlineStr"/>
       <c r="F3203" t="inlineStr"/>
       <c r="G3203" t="n">
-        <v>13695</v>
+        <v>13696</v>
       </c>
     </row>
     <row r="3204">
       <c r="A3204" t="inlineStr">
         <is>
-          <t>b97ba1c169985ba2f8043d67457868e2</t>
+          <t>7349bede20b1239120fdce3f198527ff</t>
         </is>
       </c>
       <c r="B3204" s="2" t="n">
-        <v>45731.75</v>
+        <v>45731.83333333334</v>
       </c>
       <c r="C3204" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="D3204" t="inlineStr">
         <is>
-          <t>AS Monaco</t>
+          <t>Heracles Almelo</t>
         </is>
       </c>
       <c r="E3204" t="inlineStr"/>
       <c r="F3204" t="inlineStr"/>
       <c r="G3204" t="n">
-        <v>10033</v>
+        <v>13697</v>
       </c>
     </row>
     <row r="3205">
       <c r="A3205" t="inlineStr">
         <is>
-          <t>72bbd90e1c1cf42d6eb408c43256bf3a</t>
+          <t>6b728c81ead16eb588c95454ec1de9d0</t>
         </is>
       </c>
       <c r="B3205" s="2" t="n">
-        <v>45731.79166666666</v>
+        <v>45731.83680555555</v>
       </c>
       <c r="C3205" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>RC Lens</t>
         </is>
       </c>
       <c r="D3205" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="E3205" t="inlineStr"/>
       <c r="F3205" t="inlineStr"/>
       <c r="G3205" t="n">
-        <v>13696</v>
+        <v>10034</v>
       </c>
     </row>
     <row r="3206">
       <c r="A3206" t="inlineStr">
         <is>
-          <t>7349bede20b1239120fdce3f198527ff</t>
+          <t>184cad0f1ab30f2def71bcaca5d41b3a</t>
         </is>
       </c>
       <c r="B3206" s="2" t="n">
-        <v>45731.83333333334</v>
+        <v>45732.4375</v>
       </c>
       <c r="C3206" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Çaykur Rizespor</t>
         </is>
       </c>
       <c r="D3206" t="inlineStr">
         <is>
-          <t>Heracles Almelo</t>
+          <t>Bodrum FK</t>
         </is>
       </c>
       <c r="E3206" t="inlineStr"/>
       <c r="F3206" t="inlineStr"/>
       <c r="G3206" t="n">
-        <v>13697</v>
+        <v>12326</v>
       </c>
     </row>
     <row r="3207">
       <c r="A3207" t="inlineStr">
         <is>
-          <t>6b728c81ead16eb588c95454ec1de9d0</t>
+          <t>8c396a063bfddb723325718df289bc96</t>
         </is>
       </c>
       <c r="B3207" s="2" t="n">
-        <v>45731.83680555555</v>
+        <v>45732.46875</v>
       </c>
       <c r="C3207" t="inlineStr">
         <is>
-          <t>RC Lens</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="D3207" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="E3207" t="inlineStr"/>
       <c r="F3207" t="inlineStr"/>
       <c r="G3207" t="n">
-        <v>10034</v>
+        <v>13698</v>
       </c>
     </row>
     <row r="3208">
       <c r="A3208" t="inlineStr">
         <is>
-          <t>184cad0f1ab30f2def71bcaca5d41b3a</t>
+          <t>76b3146fc114397d7e363b76f3a40440</t>
         </is>
       </c>
       <c r="B3208" s="2" t="n">
-        <v>45732.4375</v>
+        <v>45732.5625</v>
       </c>
       <c r="C3208" t="inlineStr">
         <is>
-          <t>Çaykur Rizespor</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="D3208" t="inlineStr">
         <is>
-          <t>Bodrum FK</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="E3208" t="inlineStr"/>
       <c r="F3208" t="inlineStr"/>
       <c r="G3208" t="n">
-        <v>12326</v>
+        <v>13700</v>
       </c>
     </row>
     <row r="3209">
       <c r="A3209" t="inlineStr">
         <is>
-          <t>8c396a063bfddb723325718df289bc96</t>
+          <t>3ec4e3cf8bbd9206d456e7466dc77a7b</t>
         </is>
       </c>
       <c r="B3209" s="2" t="n">
-        <v>45732.46875</v>
+        <v>45732.58333333334</v>
       </c>
       <c r="C3209" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="D3209" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="E3209" t="inlineStr"/>
       <c r="F3209" t="inlineStr"/>
       <c r="G3209" t="n">
-        <v>13698</v>
+        <v>10035</v>
       </c>
     </row>
     <row r="3210">
       <c r="A3210" t="inlineStr">
         <is>
-          <t>76b3146fc114397d7e363b76f3a40440</t>
+          <t>0b8fe229d5ccf399702dfb630aac1a4f</t>
         </is>
       </c>
       <c r="B3210" s="2" t="n">
-        <v>45732.5625</v>
+        <v>45732.65625</v>
       </c>
       <c r="C3210" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D3210" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="E3210" t="inlineStr"/>
       <c r="F3210" t="inlineStr"/>
       <c r="G3210" t="n">
-        <v>13700</v>
+        <v>13701</v>
       </c>
     </row>
     <row r="3211">
       <c r="A3211" t="inlineStr">
         <is>
-          <t>3ec4e3cf8bbd9206d456e7466dc77a7b</t>
+          <t>00fe462326c78dac442088bebf2d3550</t>
         </is>
       </c>
       <c r="B3211" s="2" t="n">
-        <v>45732.58333333334</v>
+        <v>45732.67708333334</v>
       </c>
       <c r="C3211" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="D3211" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Saint Etienne</t>
         </is>
       </c>
       <c r="E3211" t="inlineStr"/>
       <c r="F3211" t="inlineStr"/>
       <c r="G3211" t="n">
-        <v>10035</v>
+        <v>10037</v>
       </c>
     </row>
     <row r="3212">
       <c r="A3212" t="inlineStr">
         <is>
-          <t>0b8fe229d5ccf399702dfb630aac1a4f</t>
+          <t>8209e3db3b4563bba29c4042468a2170</t>
         </is>
       </c>
       <c r="B3212" s="2" t="n">
-        <v>45732.65625</v>
+        <v>45732.67708333334</v>
       </c>
       <c r="C3212" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="D3212" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Stade de Reims</t>
         </is>
       </c>
       <c r="E3212" t="inlineStr"/>
       <c r="F3212" t="inlineStr"/>
       <c r="G3212" t="n">
-        <v>13701</v>
+        <v>10036</v>
       </c>
     </row>
     <row r="3213">
       <c r="A3213" t="inlineStr">
         <is>
-          <t>00fe462326c78dac442088bebf2d3550</t>
+          <t>00c8fe4b9d37747922246b877ac87f11</t>
         </is>
       </c>
       <c r="B3213" s="2" t="n">
@@ -83227,510 +83227,510 @@
       </c>
       <c r="C3213" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="D3213" t="inlineStr">
         <is>
-          <t>Saint Etienne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="E3213" t="inlineStr"/>
       <c r="F3213" t="inlineStr"/>
       <c r="G3213" t="n">
-        <v>10037</v>
+        <v>10038</v>
       </c>
     </row>
     <row r="3214">
       <c r="A3214" t="inlineStr">
         <is>
-          <t>8209e3db3b4563bba29c4042468a2170</t>
+          <t>9e767b6b6bd5f0fe7fe3b4d2b5bfab8a</t>
         </is>
       </c>
       <c r="B3214" s="2" t="n">
-        <v>45732.67708333334</v>
+        <v>45732.82291666666</v>
       </c>
       <c r="C3214" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="D3214" t="inlineStr">
         <is>
-          <t>Stade de Reims</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="E3214" t="inlineStr"/>
       <c r="F3214" t="inlineStr"/>
       <c r="G3214" t="n">
-        <v>10036</v>
+        <v>10039</v>
       </c>
     </row>
     <row r="3215">
       <c r="A3215" t="inlineStr">
         <is>
-          <t>00c8fe4b9d37747922246b877ac87f11</t>
+          <t>3d1c81e50227e887d4ad714d671ce4c4</t>
         </is>
       </c>
       <c r="B3215" s="2" t="n">
-        <v>45732.67708333334</v>
+        <v>45744.72916666666</v>
       </c>
       <c r="C3215" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Bodrum FK</t>
         </is>
       </c>
       <c r="D3215" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Fenerbahce</t>
         </is>
       </c>
       <c r="E3215" t="inlineStr"/>
       <c r="F3215" t="inlineStr"/>
       <c r="G3215" t="n">
-        <v>10038</v>
+        <v>12332</v>
       </c>
     </row>
     <row r="3216">
       <c r="A3216" t="inlineStr">
         <is>
-          <t>9e767b6b6bd5f0fe7fe3b4d2b5bfab8a</t>
+          <t>7796df3b0735a1f2e8fac00eed1c3921</t>
         </is>
       </c>
       <c r="B3216" s="2" t="n">
-        <v>45732.82291666666</v>
+        <v>45744.82291666666</v>
       </c>
       <c r="C3216" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="D3216" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E3216" t="inlineStr"/>
       <c r="F3216" t="inlineStr"/>
       <c r="G3216" t="n">
-        <v>10039</v>
+        <v>10040</v>
       </c>
     </row>
     <row r="3217">
       <c r="A3217" t="inlineStr">
         <is>
-          <t>3d1c81e50227e887d4ad714d671ce4c4</t>
+          <t>bd3edd64cd259c96b41d24753ea9af39</t>
         </is>
       </c>
       <c r="B3217" s="2" t="n">
-        <v>45744.72916666666</v>
+        <v>45745.64583333334</v>
       </c>
       <c r="C3217" t="inlineStr">
         <is>
-          <t>Bodrum FK</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="D3217" t="inlineStr">
         <is>
-          <t>Fenerbahce</t>
-        </is>
-      </c>
-      <c r="E3217" t="inlineStr"/>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="E3217" t="inlineStr">
+        <is>
+          <t>(bd3edd64cd259c96b41d24753ea9af39,2025-03-29T15:30:00Z)</t>
+        </is>
+      </c>
       <c r="F3217" t="inlineStr"/>
       <c r="G3217" t="n">
-        <v>12332</v>
+        <v>13702</v>
       </c>
     </row>
     <row r="3218">
       <c r="A3218" t="inlineStr">
         <is>
-          <t>7796df3b0735a1f2e8fac00eed1c3921</t>
+          <t>87e2405ef095de7888ef59a6c64cd8f7</t>
         </is>
       </c>
       <c r="B3218" s="2" t="n">
-        <v>45744.82291666666</v>
+        <v>45745.66666666666</v>
       </c>
       <c r="C3218" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Stade de Reims</t>
         </is>
       </c>
       <c r="D3218" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="E3218" t="inlineStr"/>
       <c r="F3218" t="inlineStr"/>
       <c r="G3218" t="n">
-        <v>10040</v>
+        <v>10041</v>
       </c>
     </row>
     <row r="3219">
       <c r="A3219" t="inlineStr">
         <is>
-          <t>bd3edd64cd259c96b41d24753ea9af39</t>
+          <t>c5b6ce0888f1bd1f39aefa227317f7bd</t>
         </is>
       </c>
       <c r="B3219" s="2" t="n">
-        <v>45745.64583333334</v>
+        <v>45745.73958333334</v>
       </c>
       <c r="C3219" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="D3219" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="E3219" t="inlineStr">
         <is>
-          <t>(bd3edd64cd259c96b41d24753ea9af39,2025-03-29T15:30:00Z)</t>
+          <t>(c5b6ce0888f1bd1f39aefa227317f7bd,2025-03-29T17:45:00Z)</t>
         </is>
       </c>
       <c r="F3219" t="inlineStr"/>
       <c r="G3219" t="n">
-        <v>13702</v>
+        <v>13704</v>
       </c>
     </row>
     <row r="3220">
       <c r="A3220" t="inlineStr">
         <is>
-          <t>87e2405ef095de7888ef59a6c64cd8f7</t>
+          <t>83d2dbec02d152042c842024771e7fd9</t>
         </is>
       </c>
       <c r="B3220" s="2" t="n">
-        <v>45745.66666666666</v>
+        <v>45745.73958333334</v>
       </c>
       <c r="C3220" t="inlineStr">
         <is>
-          <t>Stade de Reims</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="D3220" t="inlineStr">
         <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="E3220" t="inlineStr"/>
+          <t>Almere City</t>
+        </is>
+      </c>
+      <c r="E3220" t="inlineStr">
+        <is>
+          <t>(83d2dbec02d152042c842024771e7fd9,2025-03-29T17:45:00Z)</t>
+        </is>
+      </c>
       <c r="F3220" t="inlineStr"/>
       <c r="G3220" t="n">
-        <v>10041</v>
+        <v>13703</v>
       </c>
     </row>
     <row r="3221">
       <c r="A3221" t="inlineStr">
         <is>
-          <t>c5b6ce0888f1bd1f39aefa227317f7bd</t>
+          <t>e5b1d93a82e4c63b82f63884bad40068</t>
         </is>
       </c>
       <c r="B3221" s="2" t="n">
-        <v>45745.73958333334</v>
+        <v>45745.75</v>
       </c>
       <c r="C3221" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Saint Etienne</t>
         </is>
       </c>
       <c r="D3221" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
-        </is>
-      </c>
-      <c r="E3221" t="inlineStr">
-        <is>
-          <t>(c5b6ce0888f1bd1f39aefa227317f7bd,2025-03-29T17:45:00Z)</t>
-        </is>
-      </c>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="E3221" t="inlineStr"/>
       <c r="F3221" t="inlineStr"/>
       <c r="G3221" t="n">
-        <v>13704</v>
+        <v>10042</v>
       </c>
     </row>
     <row r="3222">
       <c r="A3222" t="inlineStr">
         <is>
-          <t>83d2dbec02d152042c842024771e7fd9</t>
+          <t>551082633be7b112499f1f46c7dbcc53</t>
         </is>
       </c>
       <c r="B3222" s="2" t="n">
-        <v>45745.73958333334</v>
+        <v>45745.83333333334</v>
       </c>
       <c r="C3222" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="D3222" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="E3222" t="inlineStr">
         <is>
-          <t>(83d2dbec02d152042c842024771e7fd9,2025-03-29T17:45:00Z)</t>
+          <t>(551082633be7b112499f1f46c7dbcc53,2025-03-29T20:00:00Z)</t>
         </is>
       </c>
       <c r="F3222" t="inlineStr"/>
       <c r="G3222" t="n">
-        <v>13703</v>
+        <v>13705</v>
       </c>
     </row>
     <row r="3223">
       <c r="A3223" t="inlineStr">
         <is>
-          <t>e5b1d93a82e4c63b82f63884bad40068</t>
+          <t>957c7ab4f6f4f7f93db00bb917a373cf</t>
         </is>
       </c>
       <c r="B3223" s="2" t="n">
-        <v>45745.75</v>
+        <v>45745.83333333334</v>
       </c>
       <c r="C3223" t="inlineStr">
         <is>
-          <t>Saint Etienne</t>
+          <t>FC Zwolle</t>
         </is>
       </c>
       <c r="D3223" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="E3223" t="inlineStr"/>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="E3223" t="inlineStr">
+        <is>
+          <t>(957c7ab4f6f4f7f93db00bb917a373cf,2025-03-29T20:00:00Z)</t>
+        </is>
+      </c>
       <c r="F3223" t="inlineStr"/>
       <c r="G3223" t="n">
-        <v>10042</v>
+        <v>13706</v>
       </c>
     </row>
     <row r="3224">
       <c r="A3224" t="inlineStr">
         <is>
-          <t>551082633be7b112499f1f46c7dbcc53</t>
+          <t>eba4d4bf70b697ea685193dc0f97cb19</t>
         </is>
       </c>
       <c r="B3224" s="2" t="n">
-        <v>45745.83333333334</v>
+        <v>45745.83680555555</v>
       </c>
       <c r="C3224" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>AS Monaco</t>
         </is>
       </c>
       <c r="D3224" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
-        </is>
-      </c>
-      <c r="E3224" t="inlineStr">
-        <is>
-          <t>(551082633be7b112499f1f46c7dbcc53,2025-03-29T20:00:00Z)</t>
-        </is>
-      </c>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="E3224" t="inlineStr"/>
       <c r="F3224" t="inlineStr"/>
       <c r="G3224" t="n">
-        <v>13705</v>
+        <v>10043</v>
       </c>
     </row>
     <row r="3225">
       <c r="A3225" t="inlineStr">
         <is>
-          <t>957c7ab4f6f4f7f93db00bb917a373cf</t>
+          <t>653453467485a375abd360c686c90dbd</t>
         </is>
       </c>
       <c r="B3225" s="2" t="n">
-        <v>45745.83333333334</v>
+        <v>45746.42708333334</v>
       </c>
       <c r="C3225" t="inlineStr">
         <is>
-          <t>FC Zwolle</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="D3225" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="E3225" t="inlineStr">
         <is>
-          <t>(957c7ab4f6f4f7f93db00bb917a373cf,2025-03-29T20:00:00Z)</t>
+          <t>(653453467485a375abd360c686c90dbd,2025-03-30T10:15:00Z)</t>
         </is>
       </c>
       <c r="F3225" t="inlineStr"/>
       <c r="G3225" t="n">
-        <v>13706</v>
+        <v>13707</v>
       </c>
     </row>
     <row r="3226">
       <c r="A3226" t="inlineStr">
         <is>
-          <t>eba4d4bf70b697ea685193dc0f97cb19</t>
+          <t>8bd5ecd63219b2fd84ad50060bf99267</t>
         </is>
       </c>
       <c r="B3226" s="2" t="n">
-        <v>45745.83680555555</v>
+        <v>45746.52083333334</v>
       </c>
       <c r="C3226" t="inlineStr">
         <is>
-          <t>AS Monaco</t>
+          <t>Heracles Almelo</t>
         </is>
       </c>
       <c r="D3226" t="inlineStr">
         <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="E3226" t="inlineStr"/>
+          <t>FC Twente Enschede</t>
+        </is>
+      </c>
+      <c r="E3226" t="inlineStr">
+        <is>
+          <t>(8bd5ecd63219b2fd84ad50060bf99267,2025-03-30T12:30:00Z)</t>
+        </is>
+      </c>
       <c r="F3226" t="inlineStr"/>
       <c r="G3226" t="n">
-        <v>10043</v>
+        <v>13709</v>
       </c>
     </row>
     <row r="3227">
       <c r="A3227" t="inlineStr">
         <is>
-          <t>653453467485a375abd360c686c90dbd</t>
+          <t>9af5f9a190653694d0025404e297abd0</t>
         </is>
       </c>
       <c r="B3227" s="2" t="n">
-        <v>45746.42708333334</v>
+        <v>45746.52083333334</v>
       </c>
       <c r="C3227" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="D3227" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="E3227" t="inlineStr">
         <is>
-          <t>(653453467485a375abd360c686c90dbd,2025-03-30T10:15:00Z)</t>
+          <t>(9af5f9a190653694d0025404e297abd0,2025-03-30T12:30:00Z)</t>
         </is>
       </c>
       <c r="F3227" t="inlineStr"/>
       <c r="G3227" t="n">
-        <v>13707</v>
+        <v>13708</v>
       </c>
     </row>
     <row r="3228">
       <c r="A3228" t="inlineStr">
         <is>
-          <t>8bd5ecd63219b2fd84ad50060bf99267</t>
+          <t>568cbe59c4a293bf857302ad3440c979</t>
         </is>
       </c>
       <c r="B3228" s="2" t="n">
-        <v>45746.52083333334</v>
+        <v>45746.54166666666</v>
       </c>
       <c r="C3228" t="inlineStr">
         <is>
-          <t>Heracles Almelo</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="D3228" t="inlineStr">
         <is>
-          <t>FC Twente Enschede</t>
-        </is>
-      </c>
-      <c r="E3228" t="inlineStr">
-        <is>
-          <t>(8bd5ecd63219b2fd84ad50060bf99267,2025-03-30T12:30:00Z)</t>
-        </is>
-      </c>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="E3228" t="inlineStr"/>
       <c r="F3228" t="inlineStr"/>
       <c r="G3228" t="n">
-        <v>13709</v>
+        <v>10044</v>
       </c>
     </row>
     <row r="3229">
       <c r="A3229" t="inlineStr">
         <is>
-          <t>9af5f9a190653694d0025404e297abd0</t>
+          <t>a74acb08be26a7f31d513d0cc8355f73</t>
         </is>
       </c>
       <c r="B3229" s="2" t="n">
-        <v>45746.52083333334</v>
+        <v>45746.61458333334</v>
       </c>
       <c r="C3229" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="D3229" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="E3229" t="inlineStr">
         <is>
-          <t>(9af5f9a190653694d0025404e297abd0,2025-03-30T12:30:00Z)</t>
+          <t>(a74acb08be26a7f31d513d0cc8355f73,2025-03-30T14:45:00Z)</t>
         </is>
       </c>
       <c r="F3229" t="inlineStr"/>
       <c r="G3229" t="n">
-        <v>13708</v>
+        <v>13710</v>
       </c>
     </row>
     <row r="3230">
       <c r="A3230" t="inlineStr">
         <is>
-          <t>568cbe59c4a293bf857302ad3440c979</t>
+          <t>4d4cb056049feb2c669fe49bb235e364</t>
         </is>
       </c>
       <c r="B3230" s="2" t="n">
-        <v>45746.54166666666</v>
+        <v>45746.63541666666</v>
       </c>
       <c r="C3230" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="D3230" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="E3230" t="inlineStr"/>
       <c r="F3230" t="inlineStr"/>
       <c r="G3230" t="n">
-        <v>10044</v>
+        <v>10046</v>
       </c>
     </row>
     <row r="3231">
       <c r="A3231" t="inlineStr">
         <is>
-          <t>a74acb08be26a7f31d513d0cc8355f73</t>
+          <t>96d4454863592ac50b3b1a1259175b7d</t>
         </is>
       </c>
       <c r="B3231" s="2" t="n">
-        <v>45746.61458333334</v>
+        <v>45746.63541666666</v>
       </c>
       <c r="C3231" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="D3231" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
-        </is>
-      </c>
-      <c r="E3231" t="inlineStr">
-        <is>
-          <t>(a74acb08be26a7f31d513d0cc8355f73,2025-03-30T14:45:00Z)</t>
-        </is>
-      </c>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="E3231" t="inlineStr"/>
       <c r="F3231" t="inlineStr"/>
       <c r="G3231" t="n">
-        <v>13710</v>
+        <v>10045</v>
       </c>
     </row>
     <row r="3232">
       <c r="A3232" t="inlineStr">
         <is>
-          <t>4d4cb056049feb2c669fe49bb235e364</t>
+          <t>4ff0a4762f1009104ddab58a3139fc54</t>
         </is>
       </c>
       <c r="B3232" s="2" t="n">
@@ -83738,543 +83738,543 @@
       </c>
       <c r="C3232" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="D3232" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="E3232" t="inlineStr"/>
       <c r="F3232" t="inlineStr"/>
       <c r="G3232" t="n">
-        <v>10046</v>
+        <v>10047</v>
       </c>
     </row>
     <row r="3233">
       <c r="A3233" t="inlineStr">
         <is>
-          <t>96d4454863592ac50b3b1a1259175b7d</t>
+          <t>13d5c046adc99540ba1325dbae982d7e</t>
         </is>
       </c>
       <c r="B3233" s="2" t="n">
-        <v>45746.63541666666</v>
+        <v>45746.78125</v>
       </c>
       <c r="C3233" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="D3233" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>RC Lens</t>
         </is>
       </c>
       <c r="E3233" t="inlineStr"/>
       <c r="F3233" t="inlineStr"/>
       <c r="G3233" t="n">
-        <v>10045</v>
+        <v>10048</v>
       </c>
     </row>
     <row r="3234">
       <c r="A3234" t="inlineStr">
         <is>
-          <t>4ff0a4762f1009104ddab58a3139fc54</t>
+          <t>05eae1eb679e025e717dad1ea03f5820</t>
         </is>
       </c>
       <c r="B3234" s="2" t="n">
-        <v>45746.63541666666</v>
+        <v>45748.75</v>
       </c>
       <c r="C3234" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="D3234" t="inlineStr">
         <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="E3234" t="inlineStr"/>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="E3234" t="inlineStr">
+        <is>
+          <t>(b7320c7d9ae231bf7bb8847ca8b8741c,2025-03-09T15:45:00Z),(05eae1eb679e025e717dad1ea03f5820,2025-04-01T18:00:00Z),</t>
+        </is>
+      </c>
       <c r="F3234" t="inlineStr"/>
       <c r="G3234" t="n">
-        <v>10047</v>
+        <v>13711</v>
       </c>
     </row>
     <row r="3235">
       <c r="A3235" t="inlineStr">
         <is>
-          <t>13d5c046adc99540ba1325dbae982d7e</t>
+          <t>dd0b4194d16cca26bce95d5055c75a61</t>
         </is>
       </c>
       <c r="B3235" s="2" t="n">
-        <v>45746.78125</v>
+        <v>45749.75</v>
       </c>
       <c r="C3235" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="D3235" t="inlineStr">
         <is>
-          <t>RC Lens</t>
-        </is>
-      </c>
-      <c r="E3235" t="inlineStr"/>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="E3235" t="inlineStr">
+        <is>
+          <t>(effec3177ccfc282978781b954acb48c,2025-03-08T17:45:00Z),(dd0b4194d16cca26bce95d5055c75a61,2025-04-02T18:00:00Z),</t>
+        </is>
+      </c>
       <c r="F3235" t="inlineStr"/>
       <c r="G3235" t="n">
-        <v>10048</v>
+        <v>13712</v>
       </c>
     </row>
     <row r="3236">
       <c r="A3236" t="inlineStr">
         <is>
-          <t>05eae1eb679e025e717dad1ea03f5820</t>
+          <t>c4b2b58cb6d7e22673a0c4b4f0299999</t>
         </is>
       </c>
       <c r="B3236" s="2" t="n">
-        <v>45748.75</v>
+        <v>45751.75</v>
       </c>
       <c r="C3236" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="D3236" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="E3236" t="inlineStr">
         <is>
-          <t>(b7320c7d9ae231bf7bb8847ca8b8741c,2025-03-09T15:45:00Z),(05eae1eb679e025e717dad1ea03f5820,2025-04-01T18:00:00Z),</t>
+          <t>(c4b2b58cb6d7e22673a0c4b4f0299999,2025-04-04T18:00:00Z)</t>
         </is>
       </c>
       <c r="F3236" t="inlineStr"/>
       <c r="G3236" t="n">
-        <v>13711</v>
+        <v>13713</v>
       </c>
     </row>
     <row r="3237">
       <c r="A3237" t="inlineStr">
         <is>
-          <t>dd0b4194d16cca26bce95d5055c75a61</t>
+          <t>bd60a9d62049c544233d4a7f1a0e7355</t>
         </is>
       </c>
       <c r="B3237" s="2" t="n">
-        <v>45749.75</v>
+        <v>45751.78125</v>
       </c>
       <c r="C3237" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="D3237" t="inlineStr">
         <is>
-          <t>Groningen</t>
-        </is>
-      </c>
-      <c r="E3237" t="inlineStr">
-        <is>
-          <t>(effec3177ccfc282978781b954acb48c,2025-03-08T17:45:00Z),(dd0b4194d16cca26bce95d5055c75a61,2025-04-02T18:00:00Z),</t>
-        </is>
-      </c>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="E3237" t="inlineStr"/>
       <c r="F3237" t="inlineStr"/>
       <c r="G3237" t="n">
-        <v>13712</v>
+        <v>10049</v>
       </c>
     </row>
     <row r="3238">
       <c r="A3238" t="inlineStr">
         <is>
-          <t>c4b2b58cb6d7e22673a0c4b4f0299999</t>
+          <t>c623b4460f0b449db27e9bb27c17b50e</t>
         </is>
       </c>
       <c r="B3238" s="2" t="n">
-        <v>45751.75</v>
+        <v>45752.60416666666</v>
       </c>
       <c r="C3238" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="D3238" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="E3238" t="inlineStr">
         <is>
-          <t>(c4b2b58cb6d7e22673a0c4b4f0299999,2025-04-04T18:00:00Z)</t>
+          <t>(c623b4460f0b449db27e9bb27c17b50e,2025-04-05T14:30:00Z)</t>
         </is>
       </c>
       <c r="F3238" t="inlineStr"/>
       <c r="G3238" t="n">
-        <v>13713</v>
+        <v>13714</v>
       </c>
     </row>
     <row r="3239">
       <c r="A3239" t="inlineStr">
         <is>
-          <t>bd60a9d62049c544233d4a7f1a0e7355</t>
+          <t>58163708da32c662388661f2fb93a88e</t>
         </is>
       </c>
       <c r="B3239" s="2" t="n">
-        <v>45751.78125</v>
+        <v>45752.625</v>
       </c>
       <c r="C3239" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="D3239" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="E3239" t="inlineStr"/>
       <c r="F3239" t="inlineStr"/>
       <c r="G3239" t="n">
-        <v>10049</v>
+        <v>10050</v>
       </c>
     </row>
     <row r="3240">
       <c r="A3240" t="inlineStr">
         <is>
-          <t>c623b4460f0b449db27e9bb27c17b50e</t>
+          <t>d9fdf5bbcf41438214370773821c2308</t>
         </is>
       </c>
       <c r="B3240" s="2" t="n">
-        <v>45752.60416666666</v>
+        <v>45752.69791666666</v>
       </c>
       <c r="C3240" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>FC Twente Enschede</t>
         </is>
       </c>
       <c r="D3240" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="E3240" t="inlineStr">
         <is>
-          <t>(c623b4460f0b449db27e9bb27c17b50e,2025-04-05T14:30:00Z)</t>
+          <t>(d9fdf5bbcf41438214370773821c2308,2025-04-05T16:45:00Z)</t>
         </is>
       </c>
       <c r="F3240" t="inlineStr"/>
       <c r="G3240" t="n">
-        <v>13714</v>
+        <v>13715</v>
       </c>
     </row>
     <row r="3241">
       <c r="A3241" t="inlineStr">
         <is>
-          <t>58163708da32c662388661f2fb93a88e</t>
+          <t>16ba2967f46b6faf06eaff583a8bce4a</t>
         </is>
       </c>
       <c r="B3241" s="2" t="n">
-        <v>45752.625</v>
+        <v>45752.75</v>
       </c>
       <c r="C3241" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="D3241" t="inlineStr">
         <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="E3241" t="inlineStr"/>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="E3241" t="inlineStr">
+        <is>
+          <t>(16ba2967f46b6faf06eaff583a8bce4a,2025-04-05T18:00:00Z)</t>
+        </is>
+      </c>
       <c r="F3241" t="inlineStr"/>
       <c r="G3241" t="n">
-        <v>10050</v>
+        <v>13716</v>
       </c>
     </row>
     <row r="3242">
       <c r="A3242" t="inlineStr">
         <is>
-          <t>d9fdf5bbcf41438214370773821c2308</t>
+          <t>4ed75c8e1506cb3ae84f21eb0f788cfe</t>
         </is>
       </c>
       <c r="B3242" s="2" t="n">
-        <v>45752.69791666666</v>
+        <v>45752.79166666666</v>
       </c>
       <c r="C3242" t="inlineStr">
         <is>
-          <t>FC Twente Enschede</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="D3242" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>FC Zwolle</t>
         </is>
       </c>
       <c r="E3242" t="inlineStr">
         <is>
-          <t>(d9fdf5bbcf41438214370773821c2308,2025-04-05T16:45:00Z)</t>
+          <t>(4ed75c8e1506cb3ae84f21eb0f788cfe,2025-04-05T19:00:00Z)</t>
         </is>
       </c>
       <c r="F3242" t="inlineStr"/>
       <c r="G3242" t="n">
-        <v>13715</v>
+        <v>13717</v>
       </c>
     </row>
     <row r="3243">
       <c r="A3243" t="inlineStr">
         <is>
-          <t>16ba2967f46b6faf06eaff583a8bce4a</t>
+          <t>f79a0f3a41be8e38479bca551264e285</t>
         </is>
       </c>
       <c r="B3243" s="2" t="n">
-        <v>45752.75</v>
+        <v>45752.79513888889</v>
       </c>
       <c r="C3243" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="D3243" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
-        </is>
-      </c>
-      <c r="E3243" t="inlineStr">
-        <is>
-          <t>(16ba2967f46b6faf06eaff583a8bce4a,2025-04-05T18:00:00Z)</t>
-        </is>
-      </c>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="E3243" t="inlineStr"/>
       <c r="F3243" t="inlineStr"/>
       <c r="G3243" t="n">
-        <v>13716</v>
+        <v>10052</v>
       </c>
     </row>
     <row r="3244">
       <c r="A3244" t="inlineStr">
         <is>
-          <t>4ed75c8e1506cb3ae84f21eb0f788cfe</t>
+          <t>942701dc1be8ee6a44c60aa81c1b5a7d</t>
         </is>
       </c>
       <c r="B3244" s="2" t="n">
-        <v>45752.79166666666</v>
+        <v>45753.42708333334</v>
       </c>
       <c r="C3244" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="D3244" t="inlineStr">
         <is>
-          <t>FC Zwolle</t>
+          <t>Heracles Almelo</t>
         </is>
       </c>
       <c r="E3244" t="inlineStr">
         <is>
-          <t>(4ed75c8e1506cb3ae84f21eb0f788cfe,2025-04-05T19:00:00Z)</t>
+          <t>(942701dc1be8ee6a44c60aa81c1b5a7d,2025-04-06T10:15:00Z)</t>
         </is>
       </c>
       <c r="F3244" t="inlineStr"/>
       <c r="G3244" t="n">
-        <v>13717</v>
+        <v>13718</v>
       </c>
     </row>
     <row r="3245">
       <c r="A3245" t="inlineStr">
         <is>
-          <t>f79a0f3a41be8e38479bca551264e285</t>
+          <t>fab6288db8478823a7e662292a7d36e3</t>
         </is>
       </c>
       <c r="B3245" s="2" t="n">
-        <v>45752.79513888889</v>
+        <v>45753.4375</v>
       </c>
       <c r="C3245" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="D3245" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Bodrum FK</t>
         </is>
       </c>
       <c r="E3245" t="inlineStr"/>
       <c r="F3245" t="inlineStr"/>
       <c r="G3245" t="n">
-        <v>10052</v>
+        <v>12343</v>
       </c>
     </row>
     <row r="3246">
       <c r="A3246" t="inlineStr">
         <is>
-          <t>942701dc1be8ee6a44c60aa81c1b5a7d</t>
+          <t>8878a6aa81f2d1256543619915d7fe82</t>
         </is>
       </c>
       <c r="B3246" s="2" t="n">
-        <v>45753.42708333334</v>
+        <v>45753.52083333334</v>
       </c>
       <c r="C3246" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="D3246" t="inlineStr">
         <is>
-          <t>Heracles Almelo</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="E3246" t="inlineStr">
         <is>
-          <t>(942701dc1be8ee6a44c60aa81c1b5a7d,2025-04-06T10:15:00Z)</t>
+          <t>(8878a6aa81f2d1256543619915d7fe82,2025-04-06T12:30:00Z)</t>
         </is>
       </c>
       <c r="F3246" t="inlineStr"/>
       <c r="G3246" t="n">
-        <v>13718</v>
+        <v>13719</v>
       </c>
     </row>
     <row r="3247">
       <c r="A3247" t="inlineStr">
         <is>
-          <t>fab6288db8478823a7e662292a7d36e3</t>
+          <t>a7743d444a4618f47d28393b364be24d</t>
         </is>
       </c>
       <c r="B3247" s="2" t="n">
-        <v>45753.4375</v>
+        <v>45753.52083333334</v>
       </c>
       <c r="C3247" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="D3247" t="inlineStr">
         <is>
-          <t>Bodrum FK</t>
-        </is>
-      </c>
-      <c r="E3247" t="inlineStr"/>
+          <t>NEC Nijmegen</t>
+        </is>
+      </c>
+      <c r="E3247" t="inlineStr">
+        <is>
+          <t>(a7743d444a4618f47d28393b364be24d,2025-04-06T12:30:00Z)</t>
+        </is>
+      </c>
       <c r="F3247" t="inlineStr"/>
       <c r="G3247" t="n">
-        <v>12343</v>
+        <v>13720</v>
       </c>
     </row>
     <row r="3248">
       <c r="A3248" t="inlineStr">
         <is>
-          <t>8878a6aa81f2d1256543619915d7fe82</t>
+          <t>ea5e47a11ba783fe1237ad9c49a28fff</t>
         </is>
       </c>
       <c r="B3248" s="2" t="n">
-        <v>45753.52083333334</v>
+        <v>45753.54166666666</v>
       </c>
       <c r="C3248" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>RC Lens</t>
         </is>
       </c>
       <c r="D3248" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
-        </is>
-      </c>
-      <c r="E3248" t="inlineStr">
-        <is>
-          <t>(8878a6aa81f2d1256543619915d7fe82,2025-04-06T12:30:00Z)</t>
-        </is>
-      </c>
+          <t>Saint Etienne</t>
+        </is>
+      </c>
+      <c r="E3248" t="inlineStr"/>
       <c r="F3248" t="inlineStr"/>
       <c r="G3248" t="n">
-        <v>13719</v>
+        <v>10053</v>
       </c>
     </row>
     <row r="3249">
       <c r="A3249" t="inlineStr">
         <is>
-          <t>a7743d444a4618f47d28393b364be24d</t>
+          <t>ab3873ec4be67800d2a6c5fbeb1831cd</t>
         </is>
       </c>
       <c r="B3249" s="2" t="n">
-        <v>45753.52083333334</v>
+        <v>45753.61458333334</v>
       </c>
       <c r="C3249" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D3249" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="E3249" t="inlineStr">
         <is>
-          <t>(a7743d444a4618f47d28393b364be24d,2025-04-06T12:30:00Z)</t>
+          <t>(ab3873ec4be67800d2a6c5fbeb1831cd,2025-04-06T14:45:00Z)</t>
         </is>
       </c>
       <c r="F3249" t="inlineStr"/>
       <c r="G3249" t="n">
-        <v>13720</v>
+        <v>13721</v>
       </c>
     </row>
     <row r="3250">
       <c r="A3250" t="inlineStr">
         <is>
-          <t>ea5e47a11ba783fe1237ad9c49a28fff</t>
+          <t>c2110e2b61c8c6be124552599925b71f</t>
         </is>
       </c>
       <c r="B3250" s="2" t="n">
-        <v>45753.54166666666</v>
+        <v>45753.63541666666</v>
       </c>
       <c r="C3250" t="inlineStr">
         <is>
-          <t>RC Lens</t>
+          <t>Stade de Reims</t>
         </is>
       </c>
       <c r="D3250" t="inlineStr">
         <is>
-          <t>Saint Etienne</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="E3250" t="inlineStr"/>
       <c r="F3250" t="inlineStr"/>
       <c r="G3250" t="n">
-        <v>10053</v>
+        <v>10056</v>
       </c>
     </row>
     <row r="3251">
       <c r="A3251" t="inlineStr">
         <is>
-          <t>ab3873ec4be67800d2a6c5fbeb1831cd</t>
+          <t>97551395026657c1e16829b63fab8075</t>
         </is>
       </c>
       <c r="B3251" s="2" t="n">
-        <v>45753.61458333334</v>
+        <v>45753.63541666666</v>
       </c>
       <c r="C3251" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="D3251" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
-        </is>
-      </c>
-      <c r="E3251" t="inlineStr">
-        <is>
-          <t>(ab3873ec4be67800d2a6c5fbeb1831cd,2025-04-06T14:45:00Z)</t>
-        </is>
-      </c>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="E3251" t="inlineStr"/>
       <c r="F3251" t="inlineStr"/>
       <c r="G3251" t="n">
-        <v>13721</v>
+        <v>10055</v>
       </c>
     </row>
     <row r="3252">
       <c r="A3252" t="inlineStr">
         <is>
-          <t>c2110e2b61c8c6be124552599925b71f</t>
+          <t>127d5e6beb807bfcd6880d86a1b06ca3</t>
         </is>
       </c>
       <c r="B3252" s="2" t="n">
@@ -84282,124 +84282,124 @@
       </c>
       <c r="C3252" t="inlineStr">
         <is>
-          <t>Stade de Reims</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="D3252" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="E3252" t="inlineStr"/>
       <c r="F3252" t="inlineStr"/>
       <c r="G3252" t="n">
-        <v>10056</v>
+        <v>10054</v>
       </c>
     </row>
     <row r="3253">
       <c r="A3253" t="inlineStr">
         <is>
-          <t>97551395026657c1e16829b63fab8075</t>
+          <t>eb56b2fcc638835adafc8ac9c7610604</t>
         </is>
       </c>
       <c r="B3253" s="2" t="n">
-        <v>45753.63541666666</v>
+        <v>45753.78125</v>
       </c>
       <c r="C3253" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="D3253" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="E3253" t="inlineStr"/>
       <c r="F3253" t="inlineStr"/>
       <c r="G3253" t="n">
-        <v>10055</v>
+        <v>10057</v>
       </c>
     </row>
     <row r="3254">
       <c r="A3254" t="inlineStr">
         <is>
-          <t>127d5e6beb807bfcd6880d86a1b06ca3</t>
+          <t>f9536aad197e96f4c07b6a9b20fb5cb2</t>
         </is>
       </c>
       <c r="B3254" s="2" t="n">
-        <v>45753.63541666666</v>
+        <v>45757.69791666666</v>
       </c>
       <c r="C3254" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="D3254" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="E3254" t="inlineStr"/>
       <c r="F3254" t="inlineStr"/>
       <c r="G3254" t="n">
-        <v>10054</v>
+        <v>11111</v>
       </c>
     </row>
     <row r="3255">
       <c r="A3255" t="inlineStr">
         <is>
-          <t>eb56b2fcc638835adafc8ac9c7610604</t>
+          <t>2078f9dc44924eccf20c5a62e2112c2c</t>
         </is>
       </c>
       <c r="B3255" s="2" t="n">
-        <v>45753.78125</v>
+        <v>45757.79166666666</v>
       </c>
       <c r="C3255" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="D3255" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="E3255" t="inlineStr"/>
       <c r="F3255" t="inlineStr"/>
       <c r="G3255" t="n">
-        <v>10057</v>
+        <v>11113</v>
       </c>
     </row>
     <row r="3256">
       <c r="A3256" t="inlineStr">
         <is>
-          <t>f9536aad197e96f4c07b6a9b20fb5cb2</t>
+          <t>b7189c6bc6e4095f9327ad5d3f620482</t>
         </is>
       </c>
       <c r="B3256" s="2" t="n">
-        <v>45757.69791666666</v>
+        <v>45757.79166666666</v>
       </c>
       <c r="C3256" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="D3256" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="E3256" t="inlineStr"/>
       <c r="F3256" t="inlineStr"/>
       <c r="G3256" t="n">
-        <v>11111</v>
+        <v>11112</v>
       </c>
     </row>
     <row r="3257">
       <c r="A3257" t="inlineStr">
         <is>
-          <t>2078f9dc44924eccf20c5a62e2112c2c</t>
+          <t>0a76444300a5758686e421e5e478d558</t>
         </is>
       </c>
       <c r="B3257" s="2" t="n">
@@ -84407,585 +84407,585 @@
       </c>
       <c r="C3257" t="inlineStr">
         <is>
-          <t>NK Celje</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="D3257" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="E3257" t="inlineStr"/>
       <c r="F3257" t="inlineStr"/>
       <c r="G3257" t="n">
-        <v>11113</v>
+        <v>10817</v>
       </c>
     </row>
     <row r="3258">
       <c r="A3258" t="inlineStr">
         <is>
-          <t>b7189c6bc6e4095f9327ad5d3f620482</t>
+          <t>965be90370bb2daaed6519a9c78096a9</t>
         </is>
       </c>
       <c r="B3258" s="2" t="n">
-        <v>45757.79166666666</v>
+        <v>45758.75</v>
       </c>
       <c r="C3258" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="D3258" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
-        </is>
-      </c>
-      <c r="E3258" t="inlineStr"/>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="E3258" t="inlineStr">
+        <is>
+          <t>(965be90370bb2daaed6519a9c78096a9,2025-04-11T18:00:00Z)</t>
+        </is>
+      </c>
       <c r="F3258" t="inlineStr"/>
       <c r="G3258" t="n">
-        <v>11112</v>
+        <v>13722</v>
       </c>
     </row>
     <row r="3259">
       <c r="A3259" t="inlineStr">
         <is>
-          <t>0a76444300a5758686e421e5e478d558</t>
+          <t>e5af55601c425603fcfe86556f3bbdcc</t>
         </is>
       </c>
       <c r="B3259" s="2" t="n">
-        <v>45757.79166666666</v>
+        <v>45758.78125</v>
       </c>
       <c r="C3259" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>RC Lens</t>
         </is>
       </c>
       <c r="D3259" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Stade de Reims</t>
         </is>
       </c>
       <c r="E3259" t="inlineStr"/>
       <c r="F3259" t="inlineStr"/>
       <c r="G3259" t="n">
-        <v>10817</v>
+        <v>10058</v>
       </c>
     </row>
     <row r="3260">
       <c r="A3260" t="inlineStr">
         <is>
-          <t>965be90370bb2daaed6519a9c78096a9</t>
+          <t>f9d1e3bd5ccf7c3ae689133fda106a82</t>
         </is>
       </c>
       <c r="B3260" s="2" t="n">
-        <v>45758.75</v>
+        <v>45759.60416666666</v>
       </c>
       <c r="C3260" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="D3260" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="E3260" t="inlineStr">
         <is>
-          <t>(965be90370bb2daaed6519a9c78096a9,2025-04-11T18:00:00Z)</t>
+          <t>(f9d1e3bd5ccf7c3ae689133fda106a82,2025-04-12T14:30:00Z)</t>
         </is>
       </c>
       <c r="F3260" t="inlineStr"/>
       <c r="G3260" t="n">
-        <v>13722</v>
+        <v>13723</v>
       </c>
     </row>
     <row r="3261">
       <c r="A3261" t="inlineStr">
         <is>
-          <t>e5af55601c425603fcfe86556f3bbdcc</t>
+          <t>aa42aedcb47c8ef75bd9cb37da8dd1e0</t>
         </is>
       </c>
       <c r="B3261" s="2" t="n">
-        <v>45758.78125</v>
+        <v>45759.625</v>
       </c>
       <c r="C3261" t="inlineStr">
         <is>
-          <t>RC Lens</t>
+          <t>AS Monaco</t>
         </is>
       </c>
       <c r="D3261" t="inlineStr">
         <is>
-          <t>Stade de Reims</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="E3261" t="inlineStr"/>
       <c r="F3261" t="inlineStr"/>
       <c r="G3261" t="n">
-        <v>10058</v>
+        <v>10059</v>
       </c>
     </row>
     <row r="3262">
       <c r="A3262" t="inlineStr">
         <is>
-          <t>f9d1e3bd5ccf7c3ae689133fda106a82</t>
+          <t>b49b6a9b0247887e132edef3ea0121d2</t>
         </is>
       </c>
       <c r="B3262" s="2" t="n">
-        <v>45759.60416666666</v>
+        <v>45759.66666666666</v>
       </c>
       <c r="C3262" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Bodrum FK</t>
         </is>
       </c>
       <c r="D3262" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
-        </is>
-      </c>
-      <c r="E3262" t="inlineStr">
-        <is>
-          <t>(f9d1e3bd5ccf7c3ae689133fda106a82,2025-04-12T14:30:00Z)</t>
-        </is>
-      </c>
+          <t>Antalyaspor</t>
+        </is>
+      </c>
+      <c r="E3262" t="inlineStr"/>
       <c r="F3262" t="inlineStr"/>
       <c r="G3262" t="n">
-        <v>13723</v>
+        <v>12350</v>
       </c>
     </row>
     <row r="3263">
       <c r="A3263" t="inlineStr">
         <is>
-          <t>aa42aedcb47c8ef75bd9cb37da8dd1e0</t>
+          <t>9717700f67e8a6cf72538d5640fc97ab</t>
         </is>
       </c>
       <c r="B3263" s="2" t="n">
-        <v>45759.625</v>
+        <v>45759.69791666666</v>
       </c>
       <c r="C3263" t="inlineStr">
         <is>
-          <t>AS Monaco</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="D3263" t="inlineStr">
         <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="E3263" t="inlineStr"/>
+          <t>Heerenveen</t>
+        </is>
+      </c>
+      <c r="E3263" t="inlineStr">
+        <is>
+          <t>(9717700f67e8a6cf72538d5640fc97ab,2025-04-12T16:45:00Z)</t>
+        </is>
+      </c>
       <c r="F3263" t="inlineStr"/>
       <c r="G3263" t="n">
-        <v>10059</v>
+        <v>13724</v>
       </c>
     </row>
     <row r="3264">
       <c r="A3264" t="inlineStr">
         <is>
-          <t>b49b6a9b0247887e132edef3ea0121d2</t>
+          <t>b22447416502f58a34bebad4d53b54a1</t>
         </is>
       </c>
       <c r="B3264" s="2" t="n">
-        <v>45759.66666666666</v>
+        <v>45759.70833333334</v>
       </c>
       <c r="C3264" t="inlineStr">
         <is>
-          <t>Bodrum FK</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="D3264" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="E3264" t="inlineStr"/>
       <c r="F3264" t="inlineStr"/>
       <c r="G3264" t="n">
-        <v>12350</v>
+        <v>10060</v>
       </c>
     </row>
     <row r="3265">
       <c r="A3265" t="inlineStr">
         <is>
-          <t>9717700f67e8a6cf72538d5640fc97ab</t>
+          <t>50c465bfa44d97234657da255c9ce377</t>
         </is>
       </c>
       <c r="B3265" s="2" t="n">
-        <v>45759.69791666666</v>
+        <v>45759.75</v>
       </c>
       <c r="C3265" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="D3265" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="E3265" t="inlineStr">
         <is>
-          <t>(9717700f67e8a6cf72538d5640fc97ab,2025-04-12T16:45:00Z)</t>
+          <t>(50c465bfa44d97234657da255c9ce377,2025-04-12T18:00:00Z)</t>
         </is>
       </c>
       <c r="F3265" t="inlineStr"/>
       <c r="G3265" t="n">
-        <v>13724</v>
+        <v>13725</v>
       </c>
     </row>
     <row r="3266">
       <c r="A3266" t="inlineStr">
         <is>
-          <t>b22447416502f58a34bebad4d53b54a1</t>
+          <t>559c00affe44306109f9b3c454cee9bf</t>
         </is>
       </c>
       <c r="B3266" s="2" t="n">
-        <v>45759.70833333334</v>
+        <v>45759.79166666666</v>
       </c>
       <c r="C3266" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="D3266" t="inlineStr">
         <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="E3266" t="inlineStr"/>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="E3266" t="inlineStr">
+        <is>
+          <t>(559c00affe44306109f9b3c454cee9bf,2025-04-12T19:00:00Z)</t>
+        </is>
+      </c>
       <c r="F3266" t="inlineStr"/>
       <c r="G3266" t="n">
-        <v>10060</v>
+        <v>13726</v>
       </c>
     </row>
     <row r="3267">
       <c r="A3267" t="inlineStr">
         <is>
-          <t>50c465bfa44d97234657da255c9ce377</t>
+          <t>014219d26b06ac693edb42895d437cbb</t>
         </is>
       </c>
       <c r="B3267" s="2" t="n">
-        <v>45759.75</v>
+        <v>45759.79513888889</v>
       </c>
       <c r="C3267" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="D3267" t="inlineStr">
         <is>
-          <t>Almere City</t>
-        </is>
-      </c>
-      <c r="E3267" t="inlineStr">
-        <is>
-          <t>(50c465bfa44d97234657da255c9ce377,2025-04-12T18:00:00Z)</t>
-        </is>
-      </c>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="E3267" t="inlineStr"/>
       <c r="F3267" t="inlineStr"/>
       <c r="G3267" t="n">
-        <v>13725</v>
+        <v>10061</v>
       </c>
     </row>
     <row r="3268">
       <c r="A3268" t="inlineStr">
         <is>
-          <t>559c00affe44306109f9b3c454cee9bf</t>
+          <t>a29804cfa538173ed82a2ac03ce64593</t>
         </is>
       </c>
       <c r="B3268" s="2" t="n">
-        <v>45759.79166666666</v>
+        <v>45760.42708333334</v>
       </c>
       <c r="C3268" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="D3268" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="E3268" t="inlineStr">
         <is>
-          <t>(559c00affe44306109f9b3c454cee9bf,2025-04-12T19:00:00Z)</t>
+          <t>(a29804cfa538173ed82a2ac03ce64593,2025-04-13T10:15:00Z)</t>
         </is>
       </c>
       <c r="F3268" t="inlineStr"/>
       <c r="G3268" t="n">
-        <v>13726</v>
+        <v>13727</v>
       </c>
     </row>
     <row r="3269">
       <c r="A3269" t="inlineStr">
         <is>
-          <t>014219d26b06ac693edb42895d437cbb</t>
+          <t>d76cd398d4838aaff1a8f3aa038e6c04</t>
         </is>
       </c>
       <c r="B3269" s="2" t="n">
-        <v>45759.79513888889</v>
+        <v>45760.52083333334</v>
       </c>
       <c r="C3269" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Heracles Almelo</t>
         </is>
       </c>
       <c r="D3269" t="inlineStr">
         <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="E3269" t="inlineStr"/>
+          <t>AZ Alkmaar</t>
+        </is>
+      </c>
+      <c r="E3269" t="inlineStr">
+        <is>
+          <t>(d76cd398d4838aaff1a8f3aa038e6c04,2025-04-13T12:30:00Z)</t>
+        </is>
+      </c>
       <c r="F3269" t="inlineStr"/>
       <c r="G3269" t="n">
-        <v>10061</v>
+        <v>13728</v>
       </c>
     </row>
     <row r="3270">
       <c r="A3270" t="inlineStr">
         <is>
-          <t>a29804cfa538173ed82a2ac03ce64593</t>
+          <t>53223c77cd6a1766172ad55304419b93</t>
         </is>
       </c>
       <c r="B3270" s="2" t="n">
-        <v>45760.42708333334</v>
+        <v>45760.52083333334</v>
       </c>
       <c r="C3270" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>FC Zwolle</t>
         </is>
       </c>
       <c r="D3270" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>FC Twente Enschede</t>
         </is>
       </c>
       <c r="E3270" t="inlineStr">
         <is>
-          <t>(a29804cfa538173ed82a2ac03ce64593,2025-04-13T10:15:00Z)</t>
+          <t>(53223c77cd6a1766172ad55304419b93,2025-04-13T12:30:00Z)</t>
         </is>
       </c>
       <c r="F3270" t="inlineStr"/>
       <c r="G3270" t="n">
-        <v>13727</v>
+        <v>13729</v>
       </c>
     </row>
     <row r="3271">
       <c r="A3271" t="inlineStr">
         <is>
-          <t>d76cd398d4838aaff1a8f3aa038e6c04</t>
+          <t>ac1e4c80a1998bf5215eda7e132e9dae</t>
         </is>
       </c>
       <c r="B3271" s="2" t="n">
-        <v>45760.52083333334</v>
+        <v>45760.54166666666</v>
       </c>
       <c r="C3271" t="inlineStr">
         <is>
-          <t>Heracles Almelo</t>
+          <t>Saint Etienne</t>
         </is>
       </c>
       <c r="D3271" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
-        </is>
-      </c>
-      <c r="E3271" t="inlineStr">
-        <is>
-          <t>(d76cd398d4838aaff1a8f3aa038e6c04,2025-04-13T12:30:00Z)</t>
-        </is>
-      </c>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="E3271" t="inlineStr"/>
       <c r="F3271" t="inlineStr"/>
       <c r="G3271" t="n">
-        <v>13728</v>
+        <v>10062</v>
       </c>
     </row>
     <row r="3272">
       <c r="A3272" t="inlineStr">
         <is>
-          <t>53223c77cd6a1766172ad55304419b93</t>
+          <t>99ff3b261613ca2c8419ba627c7d653e</t>
         </is>
       </c>
       <c r="B3272" s="2" t="n">
-        <v>45760.52083333334</v>
+        <v>45760.61458333334</v>
       </c>
       <c r="C3272" t="inlineStr">
         <is>
-          <t>FC Zwolle</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="D3272" t="inlineStr">
         <is>
-          <t>FC Twente Enschede</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="E3272" t="inlineStr">
         <is>
-          <t>(53223c77cd6a1766172ad55304419b93,2025-04-13T12:30:00Z)</t>
+          <t>(99ff3b261613ca2c8419ba627c7d653e,2025-04-13T14:45:00Z)</t>
         </is>
       </c>
       <c r="F3272" t="inlineStr"/>
       <c r="G3272" t="n">
-        <v>13729</v>
+        <v>13730</v>
       </c>
     </row>
     <row r="3273">
       <c r="A3273" t="inlineStr">
         <is>
-          <t>ac1e4c80a1998bf5215eda7e132e9dae</t>
+          <t>2b51f263c4bc4060a025d8a6a3e7c5d7</t>
         </is>
       </c>
       <c r="B3273" s="2" t="n">
-        <v>45760.54166666666</v>
+        <v>45760.63541666666</v>
       </c>
       <c r="C3273" t="inlineStr">
         <is>
-          <t>Saint Etienne</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="D3273" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="E3273" t="inlineStr"/>
       <c r="F3273" t="inlineStr"/>
       <c r="G3273" t="n">
-        <v>10062</v>
+        <v>10064</v>
       </c>
     </row>
     <row r="3274">
       <c r="A3274" t="inlineStr">
         <is>
-          <t>99ff3b261613ca2c8419ba627c7d653e</t>
+          <t>07d11c11ef1ebd3b853acc411a4eaf79</t>
         </is>
       </c>
       <c r="B3274" s="2" t="n">
-        <v>45760.61458333334</v>
+        <v>45760.63541666666</v>
       </c>
       <c r="C3274" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="D3274" t="inlineStr">
         <is>
-          <t>Ajax</t>
-        </is>
-      </c>
-      <c r="E3274" t="inlineStr">
-        <is>
-          <t>(99ff3b261613ca2c8419ba627c7d653e,2025-04-13T14:45:00Z)</t>
-        </is>
-      </c>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="E3274" t="inlineStr"/>
       <c r="F3274" t="inlineStr"/>
       <c r="G3274" t="n">
-        <v>13730</v>
+        <v>10063</v>
       </c>
     </row>
     <row r="3275">
       <c r="A3275" t="inlineStr">
         <is>
-          <t>2b51f263c4bc4060a025d8a6a3e7c5d7</t>
+          <t>59442e0ca5f82a8ac672414ad296cf41</t>
         </is>
       </c>
       <c r="B3275" s="2" t="n">
-        <v>45760.63541666666</v>
+        <v>45760.78125</v>
       </c>
       <c r="C3275" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="D3275" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E3275" t="inlineStr"/>
       <c r="F3275" t="inlineStr"/>
       <c r="G3275" t="n">
-        <v>10064</v>
+        <v>10065</v>
       </c>
     </row>
     <row r="3276">
       <c r="A3276" t="inlineStr">
         <is>
-          <t>07d11c11ef1ebd3b853acc411a4eaf79</t>
+          <t>45c9ae7216c6a742798aeb2f33127b12</t>
         </is>
       </c>
       <c r="B3276" s="2" t="n">
-        <v>45760.63541666666</v>
+        <v>45764.69791666666</v>
       </c>
       <c r="C3276" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D3276" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>NK Celje</t>
         </is>
       </c>
       <c r="E3276" t="inlineStr"/>
       <c r="F3276" t="inlineStr"/>
       <c r="G3276" t="n">
-        <v>10063</v>
+        <v>11115</v>
       </c>
     </row>
     <row r="3277">
       <c r="A3277" t="inlineStr">
         <is>
-          <t>59442e0ca5f82a8ac672414ad296cf41</t>
+          <t>55143d954e89aae345a9befda8919721</t>
         </is>
       </c>
       <c r="B3277" s="2" t="n">
-        <v>45760.78125</v>
+        <v>45764.79166666666</v>
       </c>
       <c r="C3277" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="D3277" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="E3277" t="inlineStr"/>
       <c r="F3277" t="inlineStr"/>
       <c r="G3277" t="n">
-        <v>10065</v>
+        <v>11118</v>
       </c>
     </row>
     <row r="3278">
       <c r="A3278" t="inlineStr">
         <is>
-          <t>45c9ae7216c6a742798aeb2f33127b12</t>
+          <t>0ece70491b15749bf849df7816beab7e</t>
         </is>
       </c>
       <c r="B3278" s="2" t="n">
-        <v>45764.69791666666</v>
+        <v>45764.79166666666</v>
       </c>
       <c r="C3278" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="D3278" t="inlineStr">
         <is>
-          <t>NK Celje</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="E3278" t="inlineStr"/>
       <c r="F3278" t="inlineStr"/>
       <c r="G3278" t="n">
-        <v>11115</v>
+        <v>11117</v>
       </c>
     </row>
     <row r="3279">
       <c r="A3279" t="inlineStr">
         <is>
-          <t>55143d954e89aae345a9befda8919721</t>
+          <t>2f596b37853bb7120a48b601feb9268b</t>
         </is>
       </c>
       <c r="B3279" s="2" t="n">
@@ -84993,249 +84993,249 @@
       </c>
       <c r="C3279" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="D3279" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E3279" t="inlineStr"/>
       <c r="F3279" t="inlineStr"/>
       <c r="G3279" t="n">
-        <v>11118</v>
+        <v>10821</v>
       </c>
     </row>
     <row r="3280">
       <c r="A3280" t="inlineStr">
         <is>
-          <t>0ece70491b15749bf849df7816beab7e</t>
+          <t>48707ed69dbeca9ac8984905b18d8194</t>
         </is>
       </c>
       <c r="B3280" s="2" t="n">
-        <v>45764.79166666666</v>
+        <v>45765.78125</v>
       </c>
       <c r="C3280" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="D3280" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="E3280" t="inlineStr"/>
       <c r="F3280" t="inlineStr"/>
       <c r="G3280" t="n">
-        <v>11117</v>
+        <v>10066</v>
       </c>
     </row>
     <row r="3281">
       <c r="A3281" t="inlineStr">
         <is>
-          <t>2f596b37853bb7120a48b601feb9268b</t>
+          <t>8380928744f6422ffc28952daca0f8a7</t>
         </is>
       </c>
       <c r="B3281" s="2" t="n">
-        <v>45764.79166666666</v>
+        <v>45766.625</v>
       </c>
       <c r="C3281" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="D3281" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="E3281" t="inlineStr"/>
       <c r="F3281" t="inlineStr"/>
       <c r="G3281" t="n">
-        <v>10821</v>
+        <v>10067</v>
       </c>
     </row>
     <row r="3282">
       <c r="A3282" t="inlineStr">
         <is>
-          <t>48707ed69dbeca9ac8984905b18d8194</t>
+          <t>f75eebc17405850bf1268db568894944</t>
         </is>
       </c>
       <c r="B3282" s="2" t="n">
-        <v>45765.78125</v>
+        <v>45766.70833333334</v>
       </c>
       <c r="C3282" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>AS Monaco</t>
         </is>
       </c>
       <c r="D3282" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="E3282" t="inlineStr"/>
       <c r="F3282" t="inlineStr"/>
       <c r="G3282" t="n">
-        <v>10066</v>
+        <v>10068</v>
       </c>
     </row>
     <row r="3283">
       <c r="A3283" t="inlineStr">
         <is>
-          <t>8380928744f6422ffc28952daca0f8a7</t>
+          <t>2f0826f607f18829db2a8076fce31984</t>
         </is>
       </c>
       <c r="B3283" s="2" t="n">
-        <v>45766.625</v>
+        <v>45766.75</v>
       </c>
       <c r="C3283" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="D3283" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="E3283" t="inlineStr"/>
       <c r="F3283" t="inlineStr"/>
       <c r="G3283" t="n">
-        <v>10067</v>
+        <v>13731</v>
       </c>
     </row>
     <row r="3284">
       <c r="A3284" t="inlineStr">
         <is>
-          <t>f75eebc17405850bf1268db568894944</t>
+          <t>a0fc34840e1fc054da0b3dd5d42322b9</t>
         </is>
       </c>
       <c r="B3284" s="2" t="n">
-        <v>45766.70833333334</v>
+        <v>45766.79513888889</v>
       </c>
       <c r="C3284" t="inlineStr">
         <is>
-          <t>AS Monaco</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="D3284" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="E3284" t="inlineStr"/>
       <c r="F3284" t="inlineStr"/>
       <c r="G3284" t="n">
-        <v>10068</v>
+        <v>10069</v>
       </c>
     </row>
     <row r="3285">
       <c r="A3285" t="inlineStr">
         <is>
-          <t>2f0826f607f18829db2a8076fce31984</t>
+          <t>9598f6a0b6b8427e77463aeb4575cb9e</t>
         </is>
       </c>
       <c r="B3285" s="2" t="n">
-        <v>45766.75</v>
+        <v>45767.42708333334</v>
       </c>
       <c r="C3285" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="D3285" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="E3285" t="inlineStr"/>
       <c r="F3285" t="inlineStr"/>
       <c r="G3285" t="n">
-        <v>13731</v>
+        <v>13732</v>
       </c>
     </row>
     <row r="3286">
       <c r="A3286" t="inlineStr">
         <is>
-          <t>a0fc34840e1fc054da0b3dd5d42322b9</t>
+          <t>1000e3e406dcb5fcd100d006b95ba9c7</t>
         </is>
       </c>
       <c r="B3286" s="2" t="n">
-        <v>45766.79513888889</v>
+        <v>45767.54166666666</v>
       </c>
       <c r="C3286" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="D3286" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="E3286" t="inlineStr"/>
       <c r="F3286" t="inlineStr"/>
       <c r="G3286" t="n">
-        <v>10069</v>
+        <v>10070</v>
       </c>
     </row>
     <row r="3287">
       <c r="A3287" t="inlineStr">
         <is>
-          <t>9598f6a0b6b8427e77463aeb4575cb9e</t>
+          <t>52524e17875f58c8da50bbb167de28cc</t>
         </is>
       </c>
       <c r="B3287" s="2" t="n">
-        <v>45767.42708333334</v>
+        <v>45767.63541666666</v>
       </c>
       <c r="C3287" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="D3287" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>RC Lens</t>
         </is>
       </c>
       <c r="E3287" t="inlineStr"/>
       <c r="F3287" t="inlineStr"/>
       <c r="G3287" t="n">
-        <v>13732</v>
+        <v>10072</v>
       </c>
     </row>
     <row r="3288">
       <c r="A3288" t="inlineStr">
         <is>
-          <t>1000e3e406dcb5fcd100d006b95ba9c7</t>
+          <t>cd70d14abac04f9c6ade5a61fdc14a4b</t>
         </is>
       </c>
       <c r="B3288" s="2" t="n">
-        <v>45767.54166666666</v>
+        <v>45767.63541666666</v>
       </c>
       <c r="C3288" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Stade de Reims</t>
         </is>
       </c>
       <c r="D3288" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="E3288" t="inlineStr"/>
       <c r="F3288" t="inlineStr"/>
       <c r="G3288" t="n">
-        <v>10070</v>
+        <v>10073</v>
       </c>
     </row>
     <row r="3289">
       <c r="A3289" t="inlineStr">
         <is>
-          <t>52524e17875f58c8da50bbb167de28cc</t>
+          <t>a0299d1d8108fcec36c3cf4318de63a9</t>
         </is>
       </c>
       <c r="B3289" s="2" t="n">
@@ -85243,485 +85243,485 @@
       </c>
       <c r="C3289" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="D3289" t="inlineStr">
         <is>
-          <t>RC Lens</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="E3289" t="inlineStr"/>
       <c r="F3289" t="inlineStr"/>
       <c r="G3289" t="n">
-        <v>10072</v>
+        <v>10071</v>
       </c>
     </row>
     <row r="3290">
       <c r="A3290" t="inlineStr">
         <is>
-          <t>cd70d14abac04f9c6ade5a61fdc14a4b</t>
+          <t>b6f72911f5b969e38292f257f0390456</t>
         </is>
       </c>
       <c r="B3290" s="2" t="n">
-        <v>45767.63541666666</v>
+        <v>45767.78125</v>
       </c>
       <c r="C3290" t="inlineStr">
         <is>
-          <t>Stade de Reims</t>
+          <t>Saint Etienne</t>
         </is>
       </c>
       <c r="D3290" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E3290" t="inlineStr"/>
       <c r="F3290" t="inlineStr"/>
       <c r="G3290" t="n">
-        <v>10073</v>
+        <v>10074</v>
       </c>
     </row>
     <row r="3291">
       <c r="A3291" t="inlineStr">
         <is>
-          <t>a0299d1d8108fcec36c3cf4318de63a9</t>
+          <t>c4b01fbc63cd677367004ae925603159</t>
         </is>
       </c>
       <c r="B3291" s="2" t="n">
-        <v>45767.63541666666</v>
+        <v>45769.78125</v>
       </c>
       <c r="C3291" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="D3291" t="inlineStr">
         <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="E3291" t="inlineStr"/>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="E3291" t="inlineStr">
+        <is>
+          <t>(fe3e998b69783257655f70262d0f6f5a,2025-04-13T15:00:00Z)</t>
+        </is>
+      </c>
       <c r="F3291" t="inlineStr"/>
       <c r="G3291" t="n">
-        <v>10071</v>
+        <v>10075</v>
       </c>
     </row>
     <row r="3292">
       <c r="A3292" t="inlineStr">
         <is>
-          <t>b6f72911f5b969e38292f257f0390456</t>
+          <t>7026a054c418741a265d89a23df0841b</t>
         </is>
       </c>
       <c r="B3292" s="2" t="n">
-        <v>45767.78125</v>
+        <v>45770.75</v>
       </c>
       <c r="C3292" t="inlineStr">
         <is>
-          <t>Saint Etienne</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="D3292" t="inlineStr">
         <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="E3292" t="inlineStr"/>
+          <t>Heracles Almelo</t>
+        </is>
+      </c>
+      <c r="E3292" t="inlineStr">
+        <is>
+          <t>(7026a054c418741a265d89a23df0841b,2025-04-23T18:00:00Z)</t>
+        </is>
+      </c>
       <c r="F3292" t="inlineStr"/>
       <c r="G3292" t="n">
-        <v>10074</v>
+        <v>13733</v>
       </c>
     </row>
     <row r="3293">
       <c r="A3293" t="inlineStr">
         <is>
-          <t>c4b01fbc63cd677367004ae925603159</t>
+          <t>53f3a593fd22a1cbb695271f3e8746a0</t>
         </is>
       </c>
       <c r="B3293" s="2" t="n">
-        <v>45769.78125</v>
+        <v>45771.69791666666</v>
       </c>
       <c r="C3293" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="D3293" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="E3293" t="inlineStr">
         <is>
-          <t>(fe3e998b69783257655f70262d0f6f5a,2025-04-13T15:00:00Z)</t>
+          <t>(53f3a593fd22a1cbb695271f3e8746a0,2025-04-24T16:45:00Z)</t>
         </is>
       </c>
       <c r="F3293" t="inlineStr"/>
       <c r="G3293" t="n">
-        <v>10075</v>
+        <v>13734</v>
       </c>
     </row>
     <row r="3294">
       <c r="A3294" t="inlineStr">
         <is>
-          <t>7026a054c418741a265d89a23df0841b</t>
+          <t>719cbc471c7a0a63e0b883248fc37087</t>
         </is>
       </c>
       <c r="B3294" s="2" t="n">
-        <v>45770.75</v>
+        <v>45772.69791666666</v>
       </c>
       <c r="C3294" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="D3294" t="inlineStr">
         <is>
-          <t>Heracles Almelo</t>
+          <t>FC Utrecht</t>
         </is>
       </c>
       <c r="E3294" t="inlineStr">
         <is>
-          <t>(7026a054c418741a265d89a23df0841b,2025-04-23T18:00:00Z)</t>
+          <t>(719cbc471c7a0a63e0b883248fc37087,2025-04-25T16:45:00Z)</t>
         </is>
       </c>
       <c r="F3294" t="inlineStr"/>
       <c r="G3294" t="n">
-        <v>13733</v>
+        <v>13736</v>
       </c>
     </row>
     <row r="3295">
       <c r="A3295" t="inlineStr">
         <is>
-          <t>53f3a593fd22a1cbb695271f3e8746a0</t>
+          <t>15f6a57aeba3481a1bedd834d9c4585e</t>
         </is>
       </c>
       <c r="B3295" s="2" t="n">
-        <v>45771.69791666666</v>
+        <v>45772.78125</v>
       </c>
       <c r="C3295" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="D3295" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
-        </is>
-      </c>
-      <c r="E3295" t="inlineStr">
-        <is>
-          <t>(53f3a593fd22a1cbb695271f3e8746a0,2025-04-24T16:45:00Z)</t>
-        </is>
-      </c>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="E3295" t="inlineStr"/>
       <c r="F3295" t="inlineStr"/>
       <c r="G3295" t="n">
-        <v>13734</v>
+        <v>10076</v>
       </c>
     </row>
     <row r="3296">
       <c r="A3296" t="inlineStr">
         <is>
-          <t>719cbc471c7a0a63e0b883248fc37087</t>
+          <t>224cf637658c449748ffca27af288b73</t>
         </is>
       </c>
       <c r="B3296" s="2" t="n">
-        <v>45772.69791666666</v>
+        <v>45772.79166666666</v>
       </c>
       <c r="C3296" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="D3296" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>FC Zwolle</t>
         </is>
       </c>
       <c r="E3296" t="inlineStr">
         <is>
-          <t>(719cbc471c7a0a63e0b883248fc37087,2025-04-25T16:45:00Z)</t>
+          <t>(224cf637658c449748ffca27af288b73,2025-04-25T19:00:00Z)</t>
         </is>
       </c>
       <c r="F3296" t="inlineStr"/>
       <c r="G3296" t="n">
-        <v>13736</v>
+        <v>13737</v>
       </c>
     </row>
     <row r="3297">
       <c r="A3297" t="inlineStr">
         <is>
-          <t>15f6a57aeba3481a1bedd834d9c4585e</t>
+          <t>fea2005a64cbdbd80321952850fdff27</t>
         </is>
       </c>
       <c r="B3297" s="2" t="n">
-        <v>45772.78125</v>
+        <v>45773.625</v>
       </c>
       <c r="C3297" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="D3297" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Saint Etienne</t>
         </is>
       </c>
       <c r="E3297" t="inlineStr"/>
       <c r="F3297" t="inlineStr"/>
       <c r="G3297" t="n">
-        <v>10076</v>
+        <v>10077</v>
       </c>
     </row>
     <row r="3298">
       <c r="A3298" t="inlineStr">
         <is>
-          <t>224cf637658c449748ffca27af288b73</t>
+          <t>c2f1bc62470d9ae1ad54c2747bba94b4</t>
         </is>
       </c>
       <c r="B3298" s="2" t="n">
-        <v>45772.79166666666</v>
+        <v>45773.70833333334</v>
       </c>
       <c r="C3298" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="D3298" t="inlineStr">
         <is>
-          <t>FC Zwolle</t>
-        </is>
-      </c>
-      <c r="E3298" t="inlineStr">
-        <is>
-          <t>(224cf637658c449748ffca27af288b73,2025-04-25T19:00:00Z)</t>
-        </is>
-      </c>
+          <t>AS Monaco</t>
+        </is>
+      </c>
+      <c r="E3298" t="inlineStr"/>
       <c r="F3298" t="inlineStr"/>
       <c r="G3298" t="n">
-        <v>13737</v>
+        <v>10078</v>
       </c>
     </row>
     <row r="3299">
       <c r="A3299" t="inlineStr">
         <is>
-          <t>fea2005a64cbdbd80321952850fdff27</t>
+          <t>21b461ca340f56a2e993010011dd9d69</t>
         </is>
       </c>
       <c r="B3299" s="2" t="n">
-        <v>45773.625</v>
+        <v>45773.79513888889</v>
       </c>
       <c r="C3299" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="D3299" t="inlineStr">
         <is>
-          <t>Saint Etienne</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="E3299" t="inlineStr"/>
       <c r="F3299" t="inlineStr"/>
       <c r="G3299" t="n">
-        <v>10077</v>
+        <v>10079</v>
       </c>
     </row>
     <row r="3300">
       <c r="A3300" t="inlineStr">
         <is>
-          <t>c2f1bc62470d9ae1ad54c2747bba94b4</t>
+          <t>740724bb1e947598d2a404b83566969e</t>
         </is>
       </c>
       <c r="B3300" s="2" t="n">
-        <v>45773.70833333334</v>
+        <v>45774.42708333334</v>
       </c>
       <c r="C3300" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="D3300" t="inlineStr">
         <is>
-          <t>AS Monaco</t>
-        </is>
-      </c>
-      <c r="E3300" t="inlineStr"/>
+          <t>Willem II</t>
+        </is>
+      </c>
+      <c r="E3300" t="inlineStr">
+        <is>
+          <t>(740724bb1e947598d2a404b83566969e,2025-04-27T10:15:00Z)</t>
+        </is>
+      </c>
       <c r="F3300" t="inlineStr"/>
       <c r="G3300" t="n">
-        <v>10078</v>
+        <v>13738</v>
       </c>
     </row>
     <row r="3301">
       <c r="A3301" t="inlineStr">
         <is>
-          <t>21b461ca340f56a2e993010011dd9d69</t>
+          <t>f7f8a47783c66bca2728533932638d58</t>
         </is>
       </c>
       <c r="B3301" s="2" t="n">
-        <v>45773.79513888889</v>
+        <v>45774.52083333334</v>
       </c>
       <c r="C3301" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D3301" t="inlineStr">
         <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="E3301" t="inlineStr"/>
+          <t>Sparta Rotterdam</t>
+        </is>
+      </c>
+      <c r="E3301" t="inlineStr">
+        <is>
+          <t>(f7f8a47783c66bca2728533932638d58,2025-04-27T12:30:00Z)</t>
+        </is>
+      </c>
       <c r="F3301" t="inlineStr"/>
       <c r="G3301" t="n">
-        <v>10079</v>
+        <v>13739</v>
       </c>
     </row>
     <row r="3302">
       <c r="A3302" t="inlineStr">
         <is>
-          <t>740724bb1e947598d2a404b83566969e</t>
+          <t>37218ec9da830b76965c1d07013ef299</t>
         </is>
       </c>
       <c r="B3302" s="2" t="n">
-        <v>45774.42708333334</v>
+        <v>45774.52083333334</v>
       </c>
       <c r="C3302" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="D3302" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="E3302" t="inlineStr">
         <is>
-          <t>(740724bb1e947598d2a404b83566969e,2025-04-27T10:15:00Z)</t>
+          <t>(37218ec9da830b76965c1d07013ef299,2025-04-27T12:30:00Z)</t>
         </is>
       </c>
       <c r="F3302" t="inlineStr"/>
       <c r="G3302" t="n">
-        <v>13738</v>
+        <v>13740</v>
       </c>
     </row>
     <row r="3303">
       <c r="A3303" t="inlineStr">
         <is>
-          <t>f7f8a47783c66bca2728533932638d58</t>
+          <t>4939ee80f59ad0cc17bc81ec1e5d56e1</t>
         </is>
       </c>
       <c r="B3303" s="2" t="n">
-        <v>45774.52083333334</v>
+        <v>45774.54166666666</v>
       </c>
       <c r="C3303" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="D3303" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
-        </is>
-      </c>
-      <c r="E3303" t="inlineStr">
-        <is>
-          <t>(f7f8a47783c66bca2728533932638d58,2025-04-27T12:30:00Z)</t>
-        </is>
-      </c>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="E3303" t="inlineStr"/>
       <c r="F3303" t="inlineStr"/>
       <c r="G3303" t="n">
-        <v>13739</v>
+        <v>10080</v>
       </c>
     </row>
     <row r="3304">
       <c r="A3304" t="inlineStr">
         <is>
-          <t>37218ec9da830b76965c1d07013ef299</t>
+          <t>82d7306801864973232e57eb2c9a7531</t>
         </is>
       </c>
       <c r="B3304" s="2" t="n">
-        <v>45774.52083333334</v>
+        <v>45774.61458333334</v>
       </c>
       <c r="C3304" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="D3304" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="E3304" t="inlineStr">
         <is>
-          <t>(37218ec9da830b76965c1d07013ef299,2025-04-27T12:30:00Z)</t>
+          <t>(82d7306801864973232e57eb2c9a7531,2025-04-27T14:45:00Z)</t>
         </is>
       </c>
       <c r="F3304" t="inlineStr"/>
       <c r="G3304" t="n">
-        <v>13740</v>
+        <v>13741</v>
       </c>
     </row>
     <row r="3305">
       <c r="A3305" t="inlineStr">
         <is>
-          <t>4939ee80f59ad0cc17bc81ec1e5d56e1</t>
+          <t>7267064c7a26bb3a80d3d0538e4fe12f</t>
         </is>
       </c>
       <c r="B3305" s="2" t="n">
-        <v>45774.54166666666</v>
+        <v>45774.63541666666</v>
       </c>
       <c r="C3305" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="D3305" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="E3305" t="inlineStr"/>
       <c r="F3305" t="inlineStr"/>
       <c r="G3305" t="n">
-        <v>10080</v>
+        <v>10083</v>
       </c>
     </row>
     <row r="3306">
       <c r="A3306" t="inlineStr">
         <is>
-          <t>82d7306801864973232e57eb2c9a7531</t>
+          <t>75c7c61023f4be94def65bb3a50f910d</t>
         </is>
       </c>
       <c r="B3306" s="2" t="n">
-        <v>45774.61458333334</v>
+        <v>45774.63541666666</v>
       </c>
       <c r="C3306" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="D3306" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
-        </is>
-      </c>
-      <c r="E3306" t="inlineStr">
-        <is>
-          <t>(82d7306801864973232e57eb2c9a7531,2025-04-27T14:45:00Z)</t>
-        </is>
-      </c>
+          <t>Stade de Reims</t>
+        </is>
+      </c>
+      <c r="E3306" t="inlineStr"/>
       <c r="F3306" t="inlineStr"/>
       <c r="G3306" t="n">
-        <v>13741</v>
+        <v>10082</v>
       </c>
     </row>
     <row r="3307">
       <c r="A3307" t="inlineStr">
         <is>
-          <t>7267064c7a26bb3a80d3d0538e4fe12f</t>
+          <t>d29526d2e7145f43525ec0dcad7a62af</t>
         </is>
       </c>
       <c r="B3307" s="2" t="n">
@@ -85729,452 +85729,452 @@
       </c>
       <c r="C3307" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>RC Lens</t>
         </is>
       </c>
       <c r="D3307" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="E3307" t="inlineStr"/>
       <c r="F3307" t="inlineStr"/>
       <c r="G3307" t="n">
-        <v>10083</v>
+        <v>10081</v>
       </c>
     </row>
     <row r="3308">
       <c r="A3308" t="inlineStr">
         <is>
-          <t>75c7c61023f4be94def65bb3a50f910d</t>
+          <t>342583e3f4dc3884ebca35784e62c9fd</t>
         </is>
       </c>
       <c r="B3308" s="2" t="n">
-        <v>45774.63541666666</v>
+        <v>45774.78125</v>
       </c>
       <c r="C3308" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="D3308" t="inlineStr">
         <is>
-          <t>Stade de Reims</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="E3308" t="inlineStr"/>
       <c r="F3308" t="inlineStr"/>
       <c r="G3308" t="n">
-        <v>10082</v>
+        <v>10084</v>
       </c>
     </row>
     <row r="3309">
       <c r="A3309" t="inlineStr">
         <is>
-          <t>d29526d2e7145f43525ec0dcad7a62af</t>
+          <t>0a93526f02dc4d8a7aeae4e02b3c54a5</t>
         </is>
       </c>
       <c r="B3309" s="2" t="n">
-        <v>45774.63541666666</v>
+        <v>45778.5</v>
       </c>
       <c r="C3309" t="inlineStr">
         <is>
-          <t>RC Lens</t>
+          <t>Djurgardens IF</t>
         </is>
       </c>
       <c r="D3309" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="E3309" t="inlineStr"/>
       <c r="F3309" t="inlineStr"/>
       <c r="G3309" t="n">
-        <v>10081</v>
+        <v>11119</v>
       </c>
     </row>
     <row r="3310">
       <c r="A3310" t="inlineStr">
         <is>
-          <t>342583e3f4dc3884ebca35784e62c9fd</t>
+          <t>3de62d3fb97469a5f6254a829d899698</t>
         </is>
       </c>
       <c r="B3310" s="2" t="n">
-        <v>45774.78125</v>
+        <v>45779.78125</v>
       </c>
       <c r="C3310" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="D3310" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Stade de Reims</t>
         </is>
       </c>
       <c r="E3310" t="inlineStr"/>
       <c r="F3310" t="inlineStr"/>
       <c r="G3310" t="n">
-        <v>10084</v>
+        <v>10085</v>
       </c>
     </row>
     <row r="3311">
       <c r="A3311" t="inlineStr">
         <is>
-          <t>0a93526f02dc4d8a7aeae4e02b3c54a5</t>
+          <t>da5074b987a23609779170cd447a72fd</t>
         </is>
       </c>
       <c r="B3311" s="2" t="n">
-        <v>45778.5</v>
+        <v>45780.60416666666</v>
       </c>
       <c r="C3311" t="inlineStr">
         <is>
-          <t>Djurgardens IF</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="D3311" t="inlineStr">
         <is>
-          <t>Chelsea</t>
-        </is>
-      </c>
-      <c r="E3311" t="inlineStr"/>
+          <t>Willem II</t>
+        </is>
+      </c>
+      <c r="E3311" t="inlineStr">
+        <is>
+          <t>(da5074b987a23609779170cd447a72fd,2025-05-03T14:30:00Z)</t>
+        </is>
+      </c>
       <c r="F3311" t="inlineStr"/>
       <c r="G3311" t="n">
-        <v>11119</v>
+        <v>13742</v>
       </c>
     </row>
     <row r="3312">
       <c r="A3312" t="inlineStr">
         <is>
-          <t>3de62d3fb97469a5f6254a829d899698</t>
+          <t>1f126cd20bb5123412fcceb468a407b1</t>
         </is>
       </c>
       <c r="B3312" s="2" t="n">
-        <v>45779.78125</v>
+        <v>45780.625</v>
       </c>
       <c r="C3312" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="D3312" t="inlineStr">
         <is>
-          <t>Stade de Reims</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="E3312" t="inlineStr"/>
       <c r="F3312" t="inlineStr"/>
       <c r="G3312" t="n">
-        <v>10085</v>
+        <v>10086</v>
       </c>
     </row>
     <row r="3313">
       <c r="A3313" t="inlineStr">
         <is>
-          <t>da5074b987a23609779170cd447a72fd</t>
+          <t>0dae301b50ad64d298f30d84ab74bcd7</t>
         </is>
       </c>
       <c r="B3313" s="2" t="n">
-        <v>45780.60416666666</v>
+        <v>45780.69791666666</v>
       </c>
       <c r="C3313" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>Heracles Almelo</t>
         </is>
       </c>
       <c r="D3313" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="E3313" t="inlineStr">
         <is>
-          <t>(da5074b987a23609779170cd447a72fd,2025-05-03T14:30:00Z)</t>
+          <t>(0dae301b50ad64d298f30d84ab74bcd7,2025-05-03T16:45:00Z)</t>
         </is>
       </c>
       <c r="F3313" t="inlineStr"/>
       <c r="G3313" t="n">
-        <v>13742</v>
+        <v>13743</v>
       </c>
     </row>
     <row r="3314">
       <c r="A3314" t="inlineStr">
         <is>
-          <t>1f126cd20bb5123412fcceb468a407b1</t>
+          <t>159179d12ee5cf597f3b932a065f1ecf</t>
         </is>
       </c>
       <c r="B3314" s="2" t="n">
-        <v>45780.625</v>
+        <v>45780.70833333334</v>
       </c>
       <c r="C3314" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="D3314" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="E3314" t="inlineStr"/>
       <c r="F3314" t="inlineStr"/>
       <c r="G3314" t="n">
-        <v>10086</v>
+        <v>10087</v>
       </c>
     </row>
     <row r="3315">
       <c r="A3315" t="inlineStr">
         <is>
-          <t>0dae301b50ad64d298f30d84ab74bcd7</t>
+          <t>8fd0287d4794130b6a9be30d568b48b0</t>
         </is>
       </c>
       <c r="B3315" s="2" t="n">
-        <v>45780.69791666666</v>
+        <v>45780.75</v>
       </c>
       <c r="C3315" t="inlineStr">
         <is>
-          <t>Heracles Almelo</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="D3315" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="E3315" t="inlineStr">
         <is>
-          <t>(0dae301b50ad64d298f30d84ab74bcd7,2025-05-03T16:45:00Z)</t>
+          <t>(8fd0287d4794130b6a9be30d568b48b0,2025-05-03T18:00:00Z)</t>
         </is>
       </c>
       <c r="F3315" t="inlineStr"/>
       <c r="G3315" t="n">
-        <v>13743</v>
+        <v>13744</v>
       </c>
     </row>
     <row r="3316">
       <c r="A3316" t="inlineStr">
         <is>
-          <t>159179d12ee5cf597f3b932a065f1ecf</t>
+          <t>45a511e4cebbd378765c6f639e4a419e</t>
         </is>
       </c>
       <c r="B3316" s="2" t="n">
-        <v>45780.70833333334</v>
+        <v>45780.79166666666</v>
       </c>
       <c r="C3316" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>PSV Eindhoven</t>
         </is>
       </c>
       <c r="D3316" t="inlineStr">
         <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="E3316" t="inlineStr"/>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="E3316" t="inlineStr">
+        <is>
+          <t>(45a511e4cebbd378765c6f639e4a419e,2025-05-03T19:00:00Z)</t>
+        </is>
+      </c>
       <c r="F3316" t="inlineStr"/>
       <c r="G3316" t="n">
-        <v>10087</v>
+        <v>13745</v>
       </c>
     </row>
     <row r="3317">
       <c r="A3317" t="inlineStr">
         <is>
-          <t>8fd0287d4794130b6a9be30d568b48b0</t>
+          <t>a1b21b7a9d6eb863b65f9ac47af8f584</t>
         </is>
       </c>
       <c r="B3317" s="2" t="n">
-        <v>45780.75</v>
+        <v>45780.79513888889</v>
       </c>
       <c r="C3317" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Saint Etienne</t>
         </is>
       </c>
       <c r="D3317" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
-        </is>
-      </c>
-      <c r="E3317" t="inlineStr">
-        <is>
-          <t>(8fd0287d4794130b6a9be30d568b48b0,2025-05-03T18:00:00Z)</t>
-        </is>
-      </c>
+          <t>AS Monaco</t>
+        </is>
+      </c>
+      <c r="E3317" t="inlineStr"/>
       <c r="F3317" t="inlineStr"/>
       <c r="G3317" t="n">
-        <v>13744</v>
+        <v>10088</v>
       </c>
     </row>
     <row r="3318">
       <c r="A3318" t="inlineStr">
         <is>
-          <t>45a511e4cebbd378765c6f639e4a419e</t>
+          <t>bb5cfdaa82f075a6fa2092f528dc285e</t>
         </is>
       </c>
       <c r="B3318" s="2" t="n">
-        <v>45780.79166666666</v>
+        <v>45781.42708333334</v>
       </c>
       <c r="C3318" t="inlineStr">
         <is>
-          <t>PSV Eindhoven</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="D3318" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>FC Zwolle</t>
         </is>
       </c>
       <c r="E3318" t="inlineStr">
         <is>
-          <t>(45a511e4cebbd378765c6f639e4a419e,2025-05-03T19:00:00Z)</t>
+          <t>(bb5cfdaa82f075a6fa2092f528dc285e,2025-05-04T10:15:00Z)</t>
         </is>
       </c>
       <c r="F3318" t="inlineStr"/>
       <c r="G3318" t="n">
-        <v>13745</v>
+        <v>13746</v>
       </c>
     </row>
     <row r="3319">
       <c r="A3319" t="inlineStr">
         <is>
-          <t>a1b21b7a9d6eb863b65f9ac47af8f584</t>
+          <t>d0db3a17f345ee03991703b5f189afc8</t>
         </is>
       </c>
       <c r="B3319" s="2" t="n">
-        <v>45780.79513888889</v>
+        <v>45781.52083333334</v>
       </c>
       <c r="C3319" t="inlineStr">
         <is>
-          <t>Saint Etienne</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="D3319" t="inlineStr">
         <is>
-          <t>AS Monaco</t>
-        </is>
-      </c>
-      <c r="E3319" t="inlineStr"/>
+          <t>FC Twente Enschede</t>
+        </is>
+      </c>
+      <c r="E3319" t="inlineStr">
+        <is>
+          <t>(d0db3a17f345ee03991703b5f189afc8,2025-05-04T12:30:00Z)</t>
+        </is>
+      </c>
       <c r="F3319" t="inlineStr"/>
       <c r="G3319" t="n">
-        <v>10088</v>
+        <v>13748</v>
       </c>
     </row>
     <row r="3320">
       <c r="A3320" t="inlineStr">
         <is>
-          <t>bb5cfdaa82f075a6fa2092f528dc285e</t>
+          <t>c3d2fa059c2fdbccea879f49e7a02114</t>
         </is>
       </c>
       <c r="B3320" s="2" t="n">
-        <v>45781.42708333334</v>
+        <v>45781.52083333334</v>
       </c>
       <c r="C3320" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="D3320" t="inlineStr">
         <is>
-          <t>FC Zwolle</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="E3320" t="inlineStr">
         <is>
-          <t>(bb5cfdaa82f075a6fa2092f528dc285e,2025-05-04T10:15:00Z)</t>
+          <t>(c3d2fa059c2fdbccea879f49e7a02114,2025-05-04T12:30:00Z)</t>
         </is>
       </c>
       <c r="F3320" t="inlineStr"/>
       <c r="G3320" t="n">
-        <v>13746</v>
+        <v>13747</v>
       </c>
     </row>
     <row r="3321">
       <c r="A3321" t="inlineStr">
         <is>
-          <t>d0db3a17f345ee03991703b5f189afc8</t>
+          <t>d26015b07063c018620f917e59def8fb</t>
         </is>
       </c>
       <c r="B3321" s="2" t="n">
-        <v>45781.52083333334</v>
+        <v>45781.54166666666</v>
       </c>
       <c r="C3321" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="D3321" t="inlineStr">
         <is>
-          <t>FC Twente Enschede</t>
-        </is>
-      </c>
-      <c r="E3321" t="inlineStr">
-        <is>
-          <t>(d0db3a17f345ee03991703b5f189afc8,2025-05-04T12:30:00Z)</t>
-        </is>
-      </c>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="E3321" t="inlineStr"/>
       <c r="F3321" t="inlineStr"/>
       <c r="G3321" t="n">
-        <v>13748</v>
+        <v>10089</v>
       </c>
     </row>
     <row r="3322">
       <c r="A3322" t="inlineStr">
         <is>
-          <t>c3d2fa059c2fdbccea879f49e7a02114</t>
+          <t>e6afce83f8054327347fd2d657156f9f</t>
         </is>
       </c>
       <c r="B3322" s="2" t="n">
-        <v>45781.52083333334</v>
+        <v>45781.63541666666</v>
       </c>
       <c r="C3322" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="D3322" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
-        </is>
-      </c>
-      <c r="E3322" t="inlineStr">
-        <is>
-          <t>(c3d2fa059c2fdbccea879f49e7a02114,2025-05-04T12:30:00Z)</t>
-        </is>
-      </c>
+          <t>RC Lens</t>
+        </is>
+      </c>
+      <c r="E3322" t="inlineStr"/>
       <c r="F3322" t="inlineStr"/>
       <c r="G3322" t="n">
-        <v>13747</v>
+        <v>10092</v>
       </c>
     </row>
     <row r="3323">
       <c r="A3323" t="inlineStr">
         <is>
-          <t>d26015b07063c018620f917e59def8fb</t>
+          <t>9bd55e190d8d91f38ef2b3097726e3e8</t>
         </is>
       </c>
       <c r="B3323" s="2" t="n">
-        <v>45781.54166666666</v>
+        <v>45781.63541666666</v>
       </c>
       <c r="C3323" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="D3323" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="E3323" t="inlineStr"/>
       <c r="F3323" t="inlineStr"/>
       <c r="G3323" t="n">
-        <v>10089</v>
+        <v>10091</v>
       </c>
     </row>
     <row r="3324">
       <c r="A3324" t="inlineStr">
         <is>
-          <t>e6afce83f8054327347fd2d657156f9f</t>
+          <t>052515a347dd805c5fc8da6a99ecfe1e</t>
         </is>
       </c>
       <c r="B3324" s="2" t="n">
@@ -86182,174 +86182,174 @@
       </c>
       <c r="C3324" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="D3324" t="inlineStr">
         <is>
-          <t>RC Lens</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="E3324" t="inlineStr"/>
       <c r="F3324" t="inlineStr"/>
       <c r="G3324" t="n">
-        <v>10092</v>
+        <v>10090</v>
       </c>
     </row>
     <row r="3325">
       <c r="A3325" t="inlineStr">
         <is>
-          <t>9bd55e190d8d91f38ef2b3097726e3e8</t>
+          <t>abf18f705ef48f29aea2ad4b32fadb0b</t>
         </is>
       </c>
       <c r="B3325" s="2" t="n">
-        <v>45781.63541666666</v>
+        <v>45781.78125</v>
       </c>
       <c r="C3325" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="D3325" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="E3325" t="inlineStr"/>
       <c r="F3325" t="inlineStr"/>
       <c r="G3325" t="n">
-        <v>10091</v>
+        <v>10093</v>
       </c>
     </row>
     <row r="3326">
       <c r="A3326" t="inlineStr">
         <is>
-          <t>052515a347dd805c5fc8da6a99ecfe1e</t>
+          <t>1ffac73a66285a68a5e9475fa1487f53</t>
         </is>
       </c>
       <c r="B3326" s="2" t="n">
-        <v>45781.63541666666</v>
+        <v>45786.75</v>
       </c>
       <c r="C3326" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="D3326" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Heracles Almelo</t>
         </is>
       </c>
       <c r="E3326" t="inlineStr"/>
       <c r="F3326" t="inlineStr"/>
       <c r="G3326" t="n">
-        <v>10090</v>
+        <v>13749</v>
       </c>
     </row>
     <row r="3327">
       <c r="A3327" t="inlineStr">
         <is>
-          <t>abf18f705ef48f29aea2ad4b32fadb0b</t>
+          <t>43e7229b04b7d6132c911c58c1090313</t>
         </is>
       </c>
       <c r="B3327" s="2" t="n">
-        <v>45781.78125</v>
+        <v>45787.60416666666</v>
       </c>
       <c r="C3327" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="D3327" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="E3327" t="inlineStr"/>
       <c r="F3327" t="inlineStr"/>
       <c r="G3327" t="n">
-        <v>10093</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="3328">
       <c r="A3328" t="inlineStr">
         <is>
-          <t>1ffac73a66285a68a5e9475fa1487f53</t>
+          <t>7d0917d91a552249e612107b155e20d6</t>
         </is>
       </c>
       <c r="B3328" s="2" t="n">
-        <v>45786.75</v>
+        <v>45787.69791666666</v>
       </c>
       <c r="C3328" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="D3328" t="inlineStr">
         <is>
-          <t>Heracles Almelo</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="E3328" t="inlineStr"/>
       <c r="F3328" t="inlineStr"/>
       <c r="G3328" t="n">
-        <v>13749</v>
+        <v>13751</v>
       </c>
     </row>
     <row r="3329">
       <c r="A3329" t="inlineStr">
         <is>
-          <t>43e7229b04b7d6132c911c58c1090313</t>
+          <t>2a186d2dedb67903e6d7c5df0ab1987a</t>
         </is>
       </c>
       <c r="B3329" s="2" t="n">
-        <v>45787.60416666666</v>
+        <v>45787.79166666666</v>
       </c>
       <c r="C3329" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="D3329" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="E3329" t="inlineStr"/>
       <c r="F3329" t="inlineStr"/>
       <c r="G3329" t="n">
-        <v>13750</v>
+        <v>13752</v>
       </c>
     </row>
     <row r="3330">
       <c r="A3330" t="inlineStr">
         <is>
-          <t>7d0917d91a552249e612107b155e20d6</t>
+          <t>fedb3fecd801674b3b358481c4eb4495</t>
         </is>
       </c>
       <c r="B3330" s="2" t="n">
-        <v>45787.69791666666</v>
+        <v>45787.79166666666</v>
       </c>
       <c r="C3330" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="D3330" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>RC Lens</t>
         </is>
       </c>
       <c r="E3330" t="inlineStr"/>
       <c r="F3330" t="inlineStr"/>
       <c r="G3330" t="n">
-        <v>13751</v>
+        <v>10101</v>
       </c>
     </row>
     <row r="3331">
       <c r="A3331" t="inlineStr">
         <is>
-          <t>2a186d2dedb67903e6d7c5df0ab1987a</t>
+          <t>6e1225eac1b2a0fcd918f6501c2faa47</t>
         </is>
       </c>
       <c r="B3331" s="2" t="n">
@@ -86357,24 +86357,24 @@
       </c>
       <c r="C3331" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AS Monaco</t>
         </is>
       </c>
       <c r="D3331" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E3331" t="inlineStr"/>
       <c r="F3331" t="inlineStr"/>
       <c r="G3331" t="n">
-        <v>13752</v>
+        <v>10094</v>
       </c>
     </row>
     <row r="3332">
       <c r="A3332" t="inlineStr">
         <is>
-          <t>fedb3fecd801674b3b358481c4eb4495</t>
+          <t>3d771d3f0ab057397ee38d44c8e74fea</t>
         </is>
       </c>
       <c r="B3332" s="2" t="n">
@@ -86382,24 +86382,24 @@
       </c>
       <c r="C3332" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="D3332" t="inlineStr">
         <is>
-          <t>RC Lens</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="E3332" t="inlineStr"/>
       <c r="F3332" t="inlineStr"/>
       <c r="G3332" t="n">
-        <v>10101</v>
+        <v>10095</v>
       </c>
     </row>
     <row r="3333">
       <c r="A3333" t="inlineStr">
         <is>
-          <t>6e1225eac1b2a0fcd918f6501c2faa47</t>
+          <t>693a39a883bb09763ee0fffab28c6a95</t>
         </is>
       </c>
       <c r="B3333" s="2" t="n">
@@ -86407,24 +86407,24 @@
       </c>
       <c r="C3333" t="inlineStr">
         <is>
-          <t>AS Monaco</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="D3333" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="E3333" t="inlineStr"/>
       <c r="F3333" t="inlineStr"/>
       <c r="G3333" t="n">
-        <v>10094</v>
+        <v>10096</v>
       </c>
     </row>
     <row r="3334">
       <c r="A3334" t="inlineStr">
         <is>
-          <t>3d771d3f0ab057397ee38d44c8e74fea</t>
+          <t>3d30f9dd89e4a00496876f179a93a576</t>
         </is>
       </c>
       <c r="B3334" s="2" t="n">
@@ -86432,24 +86432,24 @@
       </c>
       <c r="C3334" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="D3334" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="E3334" t="inlineStr"/>
       <c r="F3334" t="inlineStr"/>
       <c r="G3334" t="n">
-        <v>10095</v>
+        <v>10098</v>
       </c>
     </row>
     <row r="3335">
       <c r="A3335" t="inlineStr">
         <is>
-          <t>693a39a883bb09763ee0fffab28c6a95</t>
+          <t>3987d244af96778c30b6cc8995ead424</t>
         </is>
       </c>
       <c r="B3335" s="2" t="n">
@@ -86457,24 +86457,24 @@
       </c>
       <c r="C3335" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="D3335" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="E3335" t="inlineStr"/>
       <c r="F3335" t="inlineStr"/>
       <c r="G3335" t="n">
-        <v>10096</v>
+        <v>10099</v>
       </c>
     </row>
     <row r="3336">
       <c r="A3336" t="inlineStr">
         <is>
-          <t>3d30f9dd89e4a00496876f179a93a576</t>
+          <t>544500f7ceef06cfeb6158896c914739</t>
         </is>
       </c>
       <c r="B3336" s="2" t="n">
@@ -86482,24 +86482,24 @@
       </c>
       <c r="C3336" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="D3336" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="E3336" t="inlineStr"/>
       <c r="F3336" t="inlineStr"/>
       <c r="G3336" t="n">
-        <v>10098</v>
+        <v>10100</v>
       </c>
     </row>
     <row r="3337">
       <c r="A3337" t="inlineStr">
         <is>
-          <t>3987d244af96778c30b6cc8995ead424</t>
+          <t>83b936811c79851e56da8ad81035e037</t>
         </is>
       </c>
       <c r="B3337" s="2" t="n">
@@ -86507,240 +86507,240 @@
       </c>
       <c r="C3337" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Stade de Reims</t>
         </is>
       </c>
       <c r="D3337" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>Saint Etienne</t>
         </is>
       </c>
       <c r="E3337" t="inlineStr"/>
       <c r="F3337" t="inlineStr"/>
       <c r="G3337" t="n">
-        <v>10099</v>
+        <v>10102</v>
       </c>
     </row>
     <row r="3338">
       <c r="A3338" t="inlineStr">
         <is>
-          <t>544500f7ceef06cfeb6158896c914739</t>
+          <t>a8dd40afc13ba9dcf9d0646f1f1d3c4a</t>
         </is>
       </c>
       <c r="B3338" s="2" t="n">
-        <v>45787.79166666666</v>
+        <v>45788.42708333334</v>
       </c>
       <c r="C3338" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>FC Zwolle</t>
         </is>
       </c>
       <c r="D3338" t="inlineStr">
         <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="E3338" t="inlineStr"/>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="E3338" t="inlineStr">
+        <is>
+          <t>(a8dd40afc13ba9dcf9d0646f1f1d3c4a,2025-05-11T10:15:00Z)</t>
+        </is>
+      </c>
       <c r="F3338" t="inlineStr"/>
       <c r="G3338" t="n">
-        <v>10100</v>
+        <v>13753</v>
       </c>
     </row>
     <row r="3339">
       <c r="A3339" t="inlineStr">
         <is>
-          <t>83b936811c79851e56da8ad81035e037</t>
+          <t>be2df2e825aadf57f446a541e03dbfba</t>
         </is>
       </c>
       <c r="B3339" s="2" t="n">
-        <v>45787.79166666666</v>
+        <v>45788.52083333334</v>
       </c>
       <c r="C3339" t="inlineStr">
         <is>
-          <t>Stade de Reims</t>
+          <t>FC Twente Enschede</t>
         </is>
       </c>
       <c r="D3339" t="inlineStr">
         <is>
-          <t>Saint Etienne</t>
-        </is>
-      </c>
-      <c r="E3339" t="inlineStr"/>
+          <t>FC Utrecht</t>
+        </is>
+      </c>
+      <c r="E3339" t="inlineStr">
+        <is>
+          <t>(be2df2e825aadf57f446a541e03dbfba,2025-05-11T12:30:00Z)</t>
+        </is>
+      </c>
       <c r="F3339" t="inlineStr"/>
       <c r="G3339" t="n">
-        <v>10102</v>
+        <v>13754</v>
       </c>
     </row>
     <row r="3340">
       <c r="A3340" t="inlineStr">
         <is>
-          <t>a8dd40afc13ba9dcf9d0646f1f1d3c4a</t>
+          <t>5dd36d4b792afdf98130d232e927322d</t>
         </is>
       </c>
       <c r="B3340" s="2" t="n">
-        <v>45788.42708333334</v>
+        <v>45788.54166666666</v>
       </c>
       <c r="C3340" t="inlineStr">
         <is>
-          <t>FC Zwolle</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="D3340" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
-        </is>
-      </c>
-      <c r="E3340" t="inlineStr">
-        <is>
-          <t>(a8dd40afc13ba9dcf9d0646f1f1d3c4a,2025-05-11T10:15:00Z)</t>
-        </is>
-      </c>
+          <t>Bodrum FK</t>
+        </is>
+      </c>
+      <c r="E3340" t="inlineStr"/>
       <c r="F3340" t="inlineStr"/>
       <c r="G3340" t="n">
-        <v>13753</v>
+        <v>12373</v>
       </c>
     </row>
     <row r="3341">
       <c r="A3341" t="inlineStr">
         <is>
-          <t>be2df2e825aadf57f446a541e03dbfba</t>
+          <t>ef00f3c4bae8b6638d11e3dbd2188082</t>
         </is>
       </c>
       <c r="B3341" s="2" t="n">
-        <v>45788.52083333334</v>
+        <v>45788.61458333334</v>
       </c>
       <c r="C3341" t="inlineStr">
         <is>
-          <t>FC Twente Enschede</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="D3341" t="inlineStr">
         <is>
-          <t>FC Utrecht</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="E3341" t="inlineStr">
         <is>
-          <t>(be2df2e825aadf57f446a541e03dbfba,2025-05-11T12:30:00Z)</t>
+          <t>(ef00f3c4bae8b6638d11e3dbd2188082,2025-05-11T14:45:00Z)</t>
         </is>
       </c>
       <c r="F3341" t="inlineStr"/>
       <c r="G3341" t="n">
-        <v>13754</v>
+        <v>13757</v>
       </c>
     </row>
     <row r="3342">
       <c r="A3342" t="inlineStr">
         <is>
-          <t>5dd36d4b792afdf98130d232e927322d</t>
+          <t>5c49b072192232bcbd344ae0c67eb378</t>
         </is>
       </c>
       <c r="B3342" s="2" t="n">
-        <v>45788.54166666666</v>
+        <v>45788.61458333334</v>
       </c>
       <c r="C3342" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="D3342" t="inlineStr">
         <is>
-          <t>Bodrum FK</t>
-        </is>
-      </c>
-      <c r="E3342" t="inlineStr"/>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="E3342" t="inlineStr">
+        <is>
+          <t>(5c49b072192232bcbd344ae0c67eb378,2025-05-11T14:45:00Z)</t>
+        </is>
+      </c>
       <c r="F3342" t="inlineStr"/>
       <c r="G3342" t="n">
-        <v>12373</v>
+        <v>13756</v>
       </c>
     </row>
     <row r="3343">
       <c r="A3343" t="inlineStr">
         <is>
-          <t>ef00f3c4bae8b6638d11e3dbd2188082</t>
+          <t>b4fedc8cc789720c5fabe4bf0a352cfb</t>
         </is>
       </c>
       <c r="B3343" s="2" t="n">
-        <v>45788.61458333334</v>
+        <v>45791.75</v>
       </c>
       <c r="C3343" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="D3343" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
-        </is>
-      </c>
-      <c r="E3343" t="inlineStr">
-        <is>
-          <t>(ef00f3c4bae8b6638d11e3dbd2188082,2025-05-11T14:45:00Z)</t>
-        </is>
-      </c>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="E3343" t="inlineStr"/>
       <c r="F3343" t="inlineStr"/>
       <c r="G3343" t="n">
-        <v>13757</v>
+        <v>13758</v>
       </c>
     </row>
     <row r="3344">
       <c r="A3344" t="inlineStr">
         <is>
-          <t>5c49b072192232bcbd344ae0c67eb378</t>
+          <t>be6d433aaebce5616c1092a518903003</t>
         </is>
       </c>
       <c r="B3344" s="2" t="n">
-        <v>45788.61458333334</v>
+        <v>45794.79166666666</v>
       </c>
       <c r="C3344" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="D3344" t="inlineStr">
         <is>
-          <t>Groningen</t>
-        </is>
-      </c>
-      <c r="E3344" t="inlineStr">
-        <is>
-          <t>(5c49b072192232bcbd344ae0c67eb378,2025-05-11T14:45:00Z)</t>
-        </is>
-      </c>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="E3344" t="inlineStr"/>
       <c r="F3344" t="inlineStr"/>
       <c r="G3344" t="n">
-        <v>13756</v>
+        <v>10107</v>
       </c>
     </row>
     <row r="3345">
       <c r="A3345" t="inlineStr">
         <is>
-          <t>b4fedc8cc789720c5fabe4bf0a352cfb</t>
+          <t>180d107e850a1873c4c20eb848ddb0eb</t>
         </is>
       </c>
       <c r="B3345" s="2" t="n">
-        <v>45791.75</v>
+        <v>45794.79166666666</v>
       </c>
       <c r="C3345" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="D3345" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Stade de Reims</t>
         </is>
       </c>
       <c r="E3345" t="inlineStr"/>
       <c r="F3345" t="inlineStr"/>
       <c r="G3345" t="n">
-        <v>13758</v>
+        <v>10108</v>
       </c>
     </row>
     <row r="3346">
       <c r="A3346" t="inlineStr">
         <is>
-          <t>be6d433aaebce5616c1092a518903003</t>
+          <t>814b16a8e8a02777de89f05130ea7b5d</t>
         </is>
       </c>
       <c r="B3346" s="2" t="n">
@@ -86748,24 +86748,24 @@
       </c>
       <c r="C3346" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="D3346" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="E3346" t="inlineStr"/>
       <c r="F3346" t="inlineStr"/>
       <c r="G3346" t="n">
-        <v>10107</v>
+        <v>10106</v>
       </c>
     </row>
     <row r="3347">
       <c r="A3347" t="inlineStr">
         <is>
-          <t>180d107e850a1873c4c20eb848ddb0eb</t>
+          <t>7aff662832f2fdb5be775923a6f92bea</t>
         </is>
       </c>
       <c r="B3347" s="2" t="n">
@@ -86773,24 +86773,24 @@
       </c>
       <c r="C3347" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="D3347" t="inlineStr">
         <is>
-          <t>Stade de Reims</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="E3347" t="inlineStr"/>
       <c r="F3347" t="inlineStr"/>
       <c r="G3347" t="n">
-        <v>10108</v>
+        <v>10105</v>
       </c>
     </row>
     <row r="3348">
       <c r="A3348" t="inlineStr">
         <is>
-          <t>814b16a8e8a02777de89f05130ea7b5d</t>
+          <t>2c7e78ff402c211af642f28ded541188</t>
         </is>
       </c>
       <c r="B3348" s="2" t="n">
@@ -86798,24 +86798,24 @@
       </c>
       <c r="C3348" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Saint Etienne</t>
         </is>
       </c>
       <c r="D3348" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="E3348" t="inlineStr"/>
       <c r="F3348" t="inlineStr"/>
       <c r="G3348" t="n">
-        <v>10106</v>
+        <v>10111</v>
       </c>
     </row>
     <row r="3349">
       <c r="A3349" t="inlineStr">
         <is>
-          <t>7aff662832f2fdb5be775923a6f92bea</t>
+          <t>dd8f9103f6f9da065308f232a4df4916</t>
         </is>
       </c>
       <c r="B3349" s="2" t="n">
@@ -86823,24 +86823,24 @@
       </c>
       <c r="C3349" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="D3349" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="E3349" t="inlineStr"/>
       <c r="F3349" t="inlineStr"/>
       <c r="G3349" t="n">
-        <v>10105</v>
+        <v>10110</v>
       </c>
     </row>
     <row r="3350">
       <c r="A3350" t="inlineStr">
         <is>
-          <t>2c7e78ff402c211af642f28ded541188</t>
+          <t>ced383aead0f26a99b5d2f1161df4aaf</t>
         </is>
       </c>
       <c r="B3350" s="2" t="n">
@@ -86848,24 +86848,24 @@
       </c>
       <c r="C3350" t="inlineStr">
         <is>
-          <t>Saint Etienne</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="D3350" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="E3350" t="inlineStr"/>
       <c r="F3350" t="inlineStr"/>
       <c r="G3350" t="n">
-        <v>10111</v>
+        <v>10109</v>
       </c>
     </row>
     <row r="3351">
       <c r="A3351" t="inlineStr">
         <is>
-          <t>dd8f9103f6f9da065308f232a4df4916</t>
+          <t>34a32d8f99c47acaef2c4fd1be4ce89e</t>
         </is>
       </c>
       <c r="B3351" s="2" t="n">
@@ -86873,24 +86873,24 @@
       </c>
       <c r="C3351" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="D3351" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="E3351" t="inlineStr"/>
       <c r="F3351" t="inlineStr"/>
       <c r="G3351" t="n">
-        <v>10110</v>
+        <v>10104</v>
       </c>
     </row>
     <row r="3352">
       <c r="A3352" t="inlineStr">
         <is>
-          <t>ced383aead0f26a99b5d2f1161df4aaf</t>
+          <t>8fb9594765c039de339cdf8f33795bbf</t>
         </is>
       </c>
       <c r="B3352" s="2" t="n">
@@ -86898,203 +86898,207 @@
       </c>
       <c r="C3352" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>RC Lens</t>
         </is>
       </c>
       <c r="D3352" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>AS Monaco</t>
         </is>
       </c>
       <c r="E3352" t="inlineStr"/>
       <c r="F3352" t="inlineStr"/>
       <c r="G3352" t="n">
-        <v>10109</v>
+        <v>10103</v>
       </c>
     </row>
     <row r="3353">
       <c r="A3353" t="inlineStr">
         <is>
-          <t>34a32d8f99c47acaef2c4fd1be4ce89e</t>
+          <t>4eee24de52e13e5cdb4d7e5c114cf3be</t>
         </is>
       </c>
       <c r="B3353" s="2" t="n">
-        <v>45794.79166666666</v>
+        <v>45798.75</v>
       </c>
       <c r="C3353" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="D3353" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Stade de Reims</t>
         </is>
       </c>
       <c r="E3353" t="inlineStr"/>
       <c r="F3353" t="inlineStr"/>
       <c r="G3353" t="n">
-        <v>10104</v>
+        <v>10112</v>
       </c>
     </row>
     <row r="3354">
       <c r="A3354" t="inlineStr">
         <is>
-          <t>8fb9594765c039de339cdf8f33795bbf</t>
+          <t>84f471b1050616157bef37ebbf16dd99</t>
         </is>
       </c>
       <c r="B3354" s="2" t="n">
-        <v>45794.79166666666</v>
+        <v>45799.69791666666</v>
       </c>
       <c r="C3354" t="inlineStr">
         <is>
-          <t>RC Lens</t>
+          <t>AZ Alkmaar</t>
         </is>
       </c>
       <c r="D3354" t="inlineStr">
         <is>
-          <t>AS Monaco</t>
-        </is>
-      </c>
-      <c r="E3354" t="inlineStr"/>
+          <t>Heerenveen</t>
+        </is>
+      </c>
+      <c r="E3354" t="inlineStr">
+        <is>
+          <t>(2e6f6cea29e992083a4b7652622d5075,2024-09-14T19:00:00Z),(2e6f6cea29e992083a4b7652622d5075,2024-09-14T19:00:00Z),</t>
+        </is>
+      </c>
       <c r="F3354" t="inlineStr"/>
       <c r="G3354" t="n">
-        <v>10103</v>
+        <v>13759</v>
       </c>
     </row>
     <row r="3355">
       <c r="A3355" t="inlineStr">
         <is>
-          <t>4eee24de52e13e5cdb4d7e5c114cf3be</t>
+          <t>77562e90dfaf8b0abb1e961dfe45f3f4</t>
         </is>
       </c>
       <c r="B3355" s="2" t="n">
-        <v>45798.75</v>
+        <v>45802.66666666666</v>
       </c>
       <c r="C3355" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="D3355" t="inlineStr">
         <is>
-          <t>Stade de Reims</t>
+          <t>Bodrum FK</t>
         </is>
       </c>
       <c r="E3355" t="inlineStr"/>
       <c r="F3355" t="inlineStr"/>
       <c r="G3355" t="n">
-        <v>10112</v>
+        <v>12383</v>
       </c>
     </row>
     <row r="3356">
       <c r="A3356" t="inlineStr">
         <is>
-          <t>84f471b1050616157bef37ebbf16dd99</t>
+          <t>e540c0d806da09787788dd358064c2cb</t>
         </is>
       </c>
       <c r="B3356" s="2" t="n">
-        <v>45799.69791666666</v>
+        <v>45806.77083333334</v>
       </c>
       <c r="C3356" t="inlineStr">
         <is>
-          <t>AZ Alkmaar</t>
+          <t>Stade de Reims</t>
         </is>
       </c>
       <c r="D3356" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
-        </is>
-      </c>
-      <c r="E3356" t="inlineStr">
-        <is>
-          <t>(2e6f6cea29e992083a4b7652622d5075,2024-09-14T19:00:00Z),(2e6f6cea29e992083a4b7652622d5075,2024-09-14T19:00:00Z),</t>
-        </is>
-      </c>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="E3356" t="inlineStr"/>
       <c r="F3356" t="inlineStr"/>
       <c r="G3356" t="n">
-        <v>13759</v>
+        <v>10113</v>
       </c>
     </row>
     <row r="3357">
       <c r="A3357" t="inlineStr">
         <is>
-          <t>77562e90dfaf8b0abb1e961dfe45f3f4</t>
+          <t>23ece6fb467752b8471453674606c656</t>
         </is>
       </c>
       <c r="B3357" s="2" t="n">
-        <v>45802.66666666666</v>
+        <v>45809.66666666666</v>
       </c>
       <c r="C3357" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Bodrum FK</t>
         </is>
       </c>
       <c r="D3357" t="inlineStr">
         <is>
-          <t>Bodrum FK</t>
+          <t>Besiktas JK</t>
         </is>
       </c>
       <c r="E3357" t="inlineStr"/>
       <c r="F3357" t="inlineStr"/>
       <c r="G3357" t="n">
-        <v>12383</v>
+        <v>12386</v>
       </c>
     </row>
     <row r="3358">
       <c r="A3358" t="inlineStr">
         <is>
-          <t>e540c0d806da09787788dd358064c2cb</t>
+          <t>d8b44175f7f154ff10771334cca58ed7</t>
         </is>
       </c>
       <c r="B3358" s="2" t="n">
-        <v>45806.77083333334</v>
+        <v>45879.70833333334</v>
       </c>
       <c r="C3358" t="inlineStr">
         <is>
-          <t>Stade de Reims</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="D3358" t="inlineStr">
         <is>
-          <t>Metz</t>
-        </is>
-      </c>
-      <c r="E3358" t="inlineStr"/>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="E3358" t="inlineStr">
+        <is>
+          <t>(f81585aab6ead4fca15221d7f08fd12e,2025-08-08T18:30:00Z)</t>
+        </is>
+      </c>
       <c r="F3358" t="inlineStr"/>
       <c r="G3358" t="n">
-        <v>10113</v>
+        <v>12392</v>
       </c>
     </row>
     <row r="3359">
       <c r="A3359" t="inlineStr">
         <is>
-          <t>23ece6fb467752b8471453674606c656</t>
+          <t>893fbbc44653ffe17114612b1a93f721</t>
         </is>
       </c>
       <c r="B3359" s="2" t="n">
-        <v>45809.66666666666</v>
+        <v>45879.70833333334</v>
       </c>
       <c r="C3359" t="inlineStr">
         <is>
-          <t>Bodrum FK</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="D3359" t="inlineStr">
         <is>
-          <t>Besiktas JK</t>
+          <t>Basaksehir</t>
         </is>
       </c>
       <c r="E3359" t="inlineStr"/>
       <c r="F3359" t="inlineStr"/>
       <c r="G3359" t="n">
-        <v>12386</v>
+        <v>12388</v>
       </c>
     </row>
     <row r="3360">
       <c r="A3360" t="inlineStr">
         <is>
-          <t>d8b44175f7f154ff10771334cca58ed7</t>
+          <t>363cd17c6dea144eec5c4419bedd0637</t>
         </is>
       </c>
       <c r="B3360" s="2" t="n">
@@ -87102,28 +87106,24 @@
       </c>
       <c r="C3360" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="D3360" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
-        </is>
-      </c>
-      <c r="E3360" t="inlineStr">
-        <is>
-          <t>(f81585aab6ead4fca15221d7f08fd12e,2025-08-08T18:30:00Z)</t>
-        </is>
-      </c>
+          <t>Besiktas JK</t>
+        </is>
+      </c>
+      <c r="E3360" t="inlineStr"/>
       <c r="F3360" t="inlineStr"/>
       <c r="G3360" t="n">
-        <v>12392</v>
+        <v>12389</v>
       </c>
     </row>
     <row r="3361">
       <c r="A3361" t="inlineStr">
         <is>
-          <t>893fbbc44653ffe17114612b1a93f721</t>
+          <t>8d1d8301e691c401282cb023421f030d</t>
         </is>
       </c>
       <c r="B3361" s="2" t="n">
@@ -87131,24 +87131,24 @@
       </c>
       <c r="C3361" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="D3361" t="inlineStr">
         <is>
-          <t>Basaksehir</t>
+          <t>Torku Konyaspor</t>
         </is>
       </c>
       <c r="E3361" t="inlineStr"/>
       <c r="F3361" t="inlineStr"/>
       <c r="G3361" t="n">
-        <v>12388</v>
+        <v>12390</v>
       </c>
     </row>
     <row r="3362">
       <c r="A3362" t="inlineStr">
         <is>
-          <t>363cd17c6dea144eec5c4419bedd0637</t>
+          <t>5be1575697e1de28067a3cee323b73a7</t>
         </is>
       </c>
       <c r="B3362" s="2" t="n">
@@ -87156,24 +87156,28 @@
       </c>
       <c r="C3362" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="D3362" t="inlineStr">
         <is>
-          <t>Besiktas JK</t>
-        </is>
-      </c>
-      <c r="E3362" t="inlineStr"/>
+          <t>Kasimpasa SK</t>
+        </is>
+      </c>
+      <c r="E3362" t="inlineStr">
+        <is>
+          <t>(b6792a45a8c7f9fcb01542f314bbfdc7,2025-08-09T18:30:00Z)</t>
+        </is>
+      </c>
       <c r="F3362" t="inlineStr"/>
       <c r="G3362" t="n">
-        <v>12389</v>
+        <v>12395</v>
       </c>
     </row>
     <row r="3363">
       <c r="A3363" t="inlineStr">
         <is>
-          <t>8d1d8301e691c401282cb023421f030d</t>
+          <t>82f9b5af11b9016c73ab78c56a4a3fd5</t>
         </is>
       </c>
       <c r="B3363" s="2" t="n">
@@ -87181,340 +87185,336 @@
       </c>
       <c r="C3363" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="D3363" t="inlineStr">
         <is>
-          <t>Torku Konyaspor</t>
-        </is>
-      </c>
-      <c r="E3363" t="inlineStr"/>
+          <t>Genclerbirligi SK</t>
+        </is>
+      </c>
+      <c r="E3363" t="inlineStr">
+        <is>
+          <t>(57b22ec9b50700a7ced874672ec43072,2025-08-09T16:00:00Z)</t>
+        </is>
+      </c>
       <c r="F3363" t="inlineStr"/>
       <c r="G3363" t="n">
-        <v>12390</v>
+        <v>12393</v>
       </c>
     </row>
     <row r="3364">
       <c r="A3364" t="inlineStr">
         <is>
-          <t>5be1575697e1de28067a3cee323b73a7</t>
+          <t>cad9816261274a90b13a0afb45a57670</t>
         </is>
       </c>
       <c r="B3364" s="2" t="n">
-        <v>45879.70833333334</v>
+        <v>45880.77083333334</v>
       </c>
       <c r="C3364" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="D3364" t="inlineStr">
         <is>
-          <t>Kasimpasa SK</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="E3364" t="inlineStr">
         <is>
-          <t>(b6792a45a8c7f9fcb01542f314bbfdc7,2025-08-09T18:30:00Z)</t>
+          <t>(b7cf8362f18bcb5d8ce3b0e2f410b316,2025-08-10T17:00:00Z)</t>
         </is>
       </c>
       <c r="F3364" t="inlineStr"/>
       <c r="G3364" t="n">
-        <v>12395</v>
+        <v>12396</v>
       </c>
     </row>
     <row r="3365">
       <c r="A3365" t="inlineStr">
         <is>
-          <t>e95b76897b8bf91d1d21273fb797ebfd</t>
+          <t>f37021de21572159764157dbf2e5ae62</t>
         </is>
       </c>
       <c r="B3365" s="2" t="n">
-        <v>45879.70833333334</v>
+        <v>45884.79166666666</v>
       </c>
       <c r="C3365" t="inlineStr">
         <is>
-          <t>Fenerbahce</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="D3365" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
-        </is>
-      </c>
-      <c r="E3365" t="inlineStr">
-        <is>
-          <t>(ea8506a66ff8adbbe2c21b4fe5909f3e,2025-08-09T18:30:00Z)</t>
-        </is>
-      </c>
+          <t>Bournemouth</t>
+        </is>
+      </c>
+      <c r="E3365" t="inlineStr"/>
       <c r="F3365" t="inlineStr"/>
       <c r="G3365" t="n">
-        <v>12394</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="3366">
       <c r="A3366" t="inlineStr">
         <is>
-          <t>82f9b5af11b9016c73ab78c56a4a3fd5</t>
+          <t>ef104c6285d1e04833a848d273a7b4ae</t>
         </is>
       </c>
       <c r="B3366" s="2" t="n">
-        <v>45879.70833333334</v>
+        <v>45885.47916666666</v>
       </c>
       <c r="C3366" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="D3366" t="inlineStr">
         <is>
-          <t>Genclerbirligi SK</t>
-        </is>
-      </c>
-      <c r="E3366" t="inlineStr">
-        <is>
-          <t>(57b22ec9b50700a7ced874672ec43072,2025-08-09T16:00:00Z)</t>
-        </is>
-      </c>
+          <t>Newcastle United</t>
+        </is>
+      </c>
+      <c r="E3366" t="inlineStr"/>
       <c r="F3366" t="inlineStr"/>
       <c r="G3366" t="n">
-        <v>12393</v>
+        <v>4701</v>
       </c>
     </row>
     <row r="3367">
       <c r="A3367" t="inlineStr">
         <is>
-          <t>2c348487fe83e32d34289637e4786691</t>
+          <t>ad4a48da31810362af7fe32298725571</t>
         </is>
       </c>
       <c r="B3367" s="2" t="n">
-        <v>45879.70833333334</v>
+        <v>45885.58333333334</v>
       </c>
       <c r="C3367" t="inlineStr">
         <is>
-          <t>Çaykur Rizespor</t>
+          <t>Brighton and Hove Albion</t>
         </is>
       </c>
       <c r="D3367" t="inlineStr">
         <is>
-          <t>Goztepe</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="E3367" t="inlineStr"/>
       <c r="F3367" t="inlineStr"/>
       <c r="G3367" t="n">
-        <v>12391</v>
+        <v>4702</v>
       </c>
     </row>
     <row r="3368">
       <c r="A3368" t="inlineStr">
         <is>
-          <t>cad9816261274a90b13a0afb45a57670</t>
+          <t>86a8812bc657e2b8c75bf77880a5cf3d</t>
         </is>
       </c>
       <c r="B3368" s="2" t="n">
-        <v>45880.77083333334</v>
+        <v>45885.58333333334</v>
       </c>
       <c r="C3368" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="D3368" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
-        </is>
-      </c>
-      <c r="E3368" t="inlineStr">
-        <is>
-          <t>(b7cf8362f18bcb5d8ce3b0e2f410b316,2025-08-10T17:00:00Z)</t>
-        </is>
-      </c>
+          <t>West Ham United</t>
+        </is>
+      </c>
+      <c r="E3368" t="inlineStr"/>
       <c r="F3368" t="inlineStr"/>
       <c r="G3368" t="n">
-        <v>12396</v>
+        <v>4704</v>
       </c>
     </row>
     <row r="3369">
       <c r="A3369" t="inlineStr">
         <is>
-          <t>f37021de21572159764157dbf2e5ae62</t>
+          <t>08ec2d2a8e67840bb3ab0e733ef2f58f</t>
         </is>
       </c>
       <c r="B3369" s="2" t="n">
-        <v>45884.79166666666</v>
+        <v>45885.58333333334</v>
       </c>
       <c r="C3369" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="D3369" t="inlineStr">
         <is>
-          <t>Bournemouth</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="E3369" t="inlineStr"/>
       <c r="F3369" t="inlineStr"/>
       <c r="G3369" t="n">
-        <v>4700</v>
+        <v>4703</v>
       </c>
     </row>
     <row r="3370">
       <c r="A3370" t="inlineStr">
         <is>
-          <t>ef104c6285d1e04833a848d273a7b4ae</t>
+          <t>52d74b5cd1e17048d446bb1cdf11916a</t>
         </is>
       </c>
       <c r="B3370" s="2" t="n">
-        <v>45885.47916666666</v>
+        <v>45885.625</v>
       </c>
       <c r="C3370" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>RC Lens</t>
         </is>
       </c>
       <c r="D3370" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E3370" t="inlineStr"/>
       <c r="F3370" t="inlineStr"/>
       <c r="G3370" t="n">
-        <v>4701</v>
+        <v>10122</v>
       </c>
     </row>
     <row r="3371">
       <c r="A3371" t="inlineStr">
         <is>
-          <t>ad4a48da31810362af7fe32298725571</t>
+          <t>7f3f540489885d028ec9395ba46ee95b</t>
         </is>
       </c>
       <c r="B3371" s="2" t="n">
-        <v>45885.58333333334</v>
+        <v>45885.6875</v>
       </c>
       <c r="C3371" t="inlineStr">
         <is>
-          <t>Brighton and Hove Albion</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="D3371" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="E3371" t="inlineStr"/>
       <c r="F3371" t="inlineStr"/>
       <c r="G3371" t="n">
-        <v>4702</v>
+        <v>4705</v>
       </c>
     </row>
     <row r="3372">
       <c r="A3372" t="inlineStr">
         <is>
-          <t>86a8812bc657e2b8c75bf77880a5cf3d</t>
+          <t>96395d8faab66cf7b72830844f66eda7</t>
         </is>
       </c>
       <c r="B3372" s="2" t="n">
-        <v>45885.58333333334</v>
+        <v>45886.54166666666</v>
       </c>
       <c r="C3372" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="D3372" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E3372" t="inlineStr"/>
       <c r="F3372" t="inlineStr"/>
       <c r="G3372" t="n">
-        <v>4704</v>
+        <v>4706</v>
       </c>
     </row>
     <row r="3373">
       <c r="A3373" t="inlineStr">
         <is>
-          <t>08ec2d2a8e67840bb3ab0e733ef2f58f</t>
+          <t>11e8905d8fd5980cf8e6ffda89470fc4</t>
         </is>
       </c>
       <c r="B3373" s="2" t="n">
-        <v>45885.58333333334</v>
+        <v>45886.54166666666</v>
       </c>
       <c r="C3373" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="D3373" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="E3373" t="inlineStr"/>
       <c r="F3373" t="inlineStr"/>
       <c r="G3373" t="n">
-        <v>4703</v>
+        <v>10117</v>
       </c>
     </row>
     <row r="3374">
       <c r="A3374" t="inlineStr">
         <is>
-          <t>52d74b5cd1e17048d446bb1cdf11916a</t>
+          <t>d6d557ea85d3e9c023d55a5a9d17c655</t>
         </is>
       </c>
       <c r="B3374" s="2" t="n">
-        <v>45885.625</v>
+        <v>45886.54166666666</v>
       </c>
       <c r="C3374" t="inlineStr">
         <is>
-          <t>RC Lens</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="D3374" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="E3374" t="inlineStr"/>
       <c r="F3374" t="inlineStr"/>
       <c r="G3374" t="n">
-        <v>10122</v>
+        <v>10115</v>
       </c>
     </row>
     <row r="3375">
       <c r="A3375" t="inlineStr">
         <is>
-          <t>7f3f540489885d028ec9395ba46ee95b</t>
+          <t>eb357add4cbd1823e64186800ab46b13</t>
         </is>
       </c>
       <c r="B3375" s="2" t="n">
-        <v>45885.6875</v>
+        <v>45886.54166666666</v>
       </c>
       <c r="C3375" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="D3375" t="inlineStr">
         <is>
-          <t>Manchester City</t>
-        </is>
-      </c>
-      <c r="E3375" t="inlineStr"/>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="E3375" t="inlineStr">
+        <is>
+          <t>(d53b160e9388a3b4ea577ff665753df0,2025-08-16T14:00:00Z)</t>
+        </is>
+      </c>
       <c r="F3375" t="inlineStr"/>
       <c r="G3375" t="n">
-        <v>4705</v>
+        <v>8587</v>
       </c>
     </row>
     <row r="3376">
       <c r="A3376" t="inlineStr">
         <is>
-          <t>96395d8faab66cf7b72830844f66eda7</t>
+          <t>8bb891813435319b6148aae3176019cc</t>
         </is>
       </c>
       <c r="B3376" s="2" t="n">
@@ -87522,24 +87522,24 @@
       </c>
       <c r="C3376" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="D3376" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="E3376" t="inlineStr"/>
       <c r="F3376" t="inlineStr"/>
       <c r="G3376" t="n">
-        <v>4706</v>
+        <v>10118</v>
       </c>
     </row>
     <row r="3377">
       <c r="A3377" t="inlineStr">
         <is>
-          <t>11e8905d8fd5980cf8e6ffda89470fc4</t>
+          <t>5e0cc0c1d95a82efdfa5b8fdfab19617</t>
         </is>
       </c>
       <c r="B3377" s="2" t="n">
@@ -87547,24 +87547,28 @@
       </c>
       <c r="C3377" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="D3377" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="E3377" t="inlineStr"/>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="E3377" t="inlineStr">
+        <is>
+          <t>(3416268fbd4e7145b06aee2a0d4051bb,2025-08-15T18:45:00Z)</t>
+        </is>
+      </c>
       <c r="F3377" t="inlineStr"/>
       <c r="G3377" t="n">
-        <v>10117</v>
+        <v>10119</v>
       </c>
     </row>
     <row r="3378">
       <c r="A3378" t="inlineStr">
         <is>
-          <t>d6d557ea85d3e9c023d55a5a9d17c655</t>
+          <t>35575f2cd5687181a5f79dcaeb37408c</t>
         </is>
       </c>
       <c r="B3378" s="2" t="n">
@@ -87572,24 +87576,28 @@
       </c>
       <c r="C3378" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>AS Monaco</t>
         </is>
       </c>
       <c r="D3378" t="inlineStr">
         <is>
-          <t>Lorient</t>
-        </is>
-      </c>
-      <c r="E3378" t="inlineStr"/>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="E3378" t="inlineStr">
+        <is>
+          <t>(570c8ff9509c7981e1d9f257e2a19267,2025-08-16T17:00:00Z)</t>
+        </is>
+      </c>
       <c r="F3378" t="inlineStr"/>
       <c r="G3378" t="n">
-        <v>10115</v>
+        <v>10120</v>
       </c>
     </row>
     <row r="3379">
       <c r="A3379" t="inlineStr">
         <is>
-          <t>a0775198ed65a25646a663f75d3eda26</t>
+          <t>7d46b3d24c88845c6de2e820955527f3</t>
         </is>
       </c>
       <c r="B3379" s="2" t="n">
@@ -87597,24 +87605,28 @@
       </c>
       <c r="C3379" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="D3379" t="inlineStr">
         <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="E3379" t="inlineStr"/>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="E3379" t="inlineStr">
+        <is>
+          <t>(3708a0b105707e447d8057ff0309104f,2025-08-16T19:05:00Z)</t>
+        </is>
+      </c>
       <c r="F3379" t="inlineStr"/>
       <c r="G3379" t="n">
-        <v>10116</v>
+        <v>10121</v>
       </c>
     </row>
     <row r="3380">
       <c r="A3380" t="inlineStr">
         <is>
-          <t>eb357add4cbd1823e64186800ab46b13</t>
+          <t>fdd9fa9a13ffbcc0e5948c36805e79f7</t>
         </is>
       </c>
       <c r="B3380" s="2" t="n">
@@ -87622,240 +87634,224 @@
       </c>
       <c r="C3380" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="D3380" t="inlineStr">
         <is>
-          <t>Brentford</t>
-        </is>
-      </c>
-      <c r="E3380" t="inlineStr">
-        <is>
-          <t>(d53b160e9388a3b4ea577ff665753df0,2025-08-16T14:00:00Z)</t>
-        </is>
-      </c>
+          <t>Paris FC</t>
+        </is>
+      </c>
+      <c r="E3380" t="inlineStr"/>
       <c r="F3380" t="inlineStr"/>
       <c r="G3380" t="n">
-        <v>8587</v>
+        <v>10114</v>
       </c>
     </row>
     <row r="3381">
       <c r="A3381" t="inlineStr">
         <is>
-          <t>8bb891813435319b6148aae3176019cc</t>
+          <t>4c489c20064afdb4a5623dff80c6c2d7</t>
         </is>
       </c>
       <c r="B3381" s="2" t="n">
-        <v>45886.54166666666</v>
+        <v>45886.64583333334</v>
       </c>
       <c r="C3381" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="D3381" t="inlineStr">
         <is>
-          <t>Paris Saint Germain</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="E3381" t="inlineStr"/>
       <c r="F3381" t="inlineStr"/>
       <c r="G3381" t="n">
-        <v>10118</v>
+        <v>4707</v>
       </c>
     </row>
     <row r="3382">
       <c r="A3382" t="inlineStr">
         <is>
-          <t>5e0cc0c1d95a82efdfa5b8fdfab19617</t>
+          <t>92020926e46ec2ebdc748d01a37a17b2</t>
         </is>
       </c>
       <c r="B3382" s="2" t="n">
-        <v>45886.54166666666</v>
+        <v>45887.79166666666</v>
       </c>
       <c r="C3382" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="D3382" t="inlineStr">
         <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="E3382" t="inlineStr">
-        <is>
-          <t>(3416268fbd4e7145b06aee2a0d4051bb,2025-08-15T18:45:00Z)</t>
-        </is>
-      </c>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="E3382" t="inlineStr"/>
       <c r="F3382" t="inlineStr"/>
       <c r="G3382" t="n">
-        <v>10119</v>
+        <v>4708</v>
       </c>
     </row>
     <row r="3383">
       <c r="A3383" t="inlineStr">
         <is>
-          <t>35575f2cd5687181a5f79dcaeb37408c</t>
+          <t>b7595997eb85dcbc3a4e4eb020f315dd</t>
         </is>
       </c>
       <c r="B3383" s="2" t="n">
-        <v>45886.54166666666</v>
+        <v>45891.77083333334</v>
       </c>
       <c r="C3383" t="inlineStr">
         <is>
-          <t>AS Monaco</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="D3383" t="inlineStr">
         <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="E3383" t="inlineStr">
-        <is>
-          <t>(570c8ff9509c7981e1d9f257e2a19267,2025-08-16T17:00:00Z)</t>
-        </is>
-      </c>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="E3383" t="inlineStr"/>
       <c r="F3383" t="inlineStr"/>
       <c r="G3383" t="n">
-        <v>10120</v>
+        <v>6183</v>
       </c>
     </row>
     <row r="3384">
       <c r="A3384" t="inlineStr">
         <is>
-          <t>7d46b3d24c88845c6de2e820955527f3</t>
+          <t>d17accb4fb59e0c9b4af9a7328e3b265</t>
         </is>
       </c>
       <c r="B3384" s="2" t="n">
-        <v>45886.54166666666</v>
+        <v>45892.5625</v>
       </c>
       <c r="C3384" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="D3384" t="inlineStr">
         <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="E3384" t="inlineStr">
-        <is>
-          <t>(3708a0b105707e447d8057ff0309104f,2025-08-16T19:05:00Z)</t>
-        </is>
-      </c>
+          <t>VfB Stuttgart</t>
+        </is>
+      </c>
+      <c r="E3384" t="inlineStr"/>
       <c r="F3384" t="inlineStr"/>
       <c r="G3384" t="n">
-        <v>10121</v>
+        <v>6191</v>
       </c>
     </row>
     <row r="3385">
       <c r="A3385" t="inlineStr">
         <is>
-          <t>fdd9fa9a13ffbcc0e5948c36805e79f7</t>
+          <t>8a9a476c07fc5ec49a8aaf314e9dd632</t>
         </is>
       </c>
       <c r="B3385" s="2" t="n">
-        <v>45886.54166666666</v>
+        <v>45892.5625</v>
       </c>
       <c r="C3385" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>FC St. Pauli</t>
         </is>
       </c>
       <c r="D3385" t="inlineStr">
         <is>
-          <t>Paris FC</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="E3385" t="inlineStr"/>
       <c r="F3385" t="inlineStr"/>
       <c r="G3385" t="n">
-        <v>10114</v>
+        <v>6188</v>
       </c>
     </row>
     <row r="3386">
       <c r="A3386" t="inlineStr">
         <is>
-          <t>4c489c20064afdb4a5623dff80c6c2d7</t>
+          <t>2b9ab502221f28a483bd6e15c912aa8a</t>
         </is>
       </c>
       <c r="B3386" s="2" t="n">
-        <v>45886.64583333334</v>
+        <v>45892.5625</v>
       </c>
       <c r="C3386" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>1. FC Heidenheim</t>
         </is>
       </c>
       <c r="D3386" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>VfL Wolfsburg</t>
         </is>
       </c>
       <c r="E3386" t="inlineStr"/>
       <c r="F3386" t="inlineStr"/>
       <c r="G3386" t="n">
-        <v>4707</v>
+        <v>6184</v>
       </c>
     </row>
     <row r="3387">
       <c r="A3387" t="inlineStr">
         <is>
-          <t>92020926e46ec2ebdc748d01a37a17b2</t>
+          <t>45c1a5890b03f21bc137340dabc4a7d3</t>
         </is>
       </c>
       <c r="B3387" s="2" t="n">
-        <v>45887.79166666666</v>
+        <v>45892.5625</v>
       </c>
       <c r="C3387" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>SC Freiburg</t>
         </is>
       </c>
       <c r="D3387" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="E3387" t="inlineStr"/>
       <c r="F3387" t="inlineStr"/>
       <c r="G3387" t="n">
-        <v>4708</v>
+        <v>6186</v>
       </c>
     </row>
     <row r="3388">
       <c r="A3388" t="inlineStr">
         <is>
-          <t>b7595997eb85dcbc3a4e4eb020f315dd</t>
+          <t>5b2fff8ea253f0c94af5756895b7f149</t>
         </is>
       </c>
       <c r="B3388" s="2" t="n">
-        <v>45891.77083333334</v>
+        <v>45892.5625</v>
       </c>
       <c r="C3388" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>FSV Mainz 05</t>
         </is>
       </c>
       <c r="D3388" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>1. FC Köln</t>
         </is>
       </c>
       <c r="E3388" t="inlineStr"/>
       <c r="F3388" t="inlineStr"/>
       <c r="G3388" t="n">
-        <v>6183</v>
+        <v>6185</v>
       </c>
     </row>
     <row r="3389">
       <c r="A3389" t="inlineStr">
         <is>
-          <t>d17accb4fb59e0c9b4af9a7328e3b265</t>
+          <t>a81fc1a653444c18ddbfa894d842571c</t>
         </is>
       </c>
       <c r="B3389" s="2" t="n">
@@ -87863,24 +87859,24 @@
       </c>
       <c r="C3389" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="D3389" t="inlineStr">
         <is>
-          <t>VfB Stuttgart</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="E3389" t="inlineStr"/>
       <c r="F3389" t="inlineStr"/>
       <c r="G3389" t="n">
-        <v>6191</v>
+        <v>6190</v>
       </c>
     </row>
     <row r="3390">
       <c r="A3390" t="inlineStr">
         <is>
-          <t>8a9a476c07fc5ec49a8aaf314e9dd632</t>
+          <t>4b5bf052ddefb56d61c95922406bfa13</t>
         </is>
       </c>
       <c r="B3390" s="2" t="n">
@@ -87888,24 +87884,24 @@
       </c>
       <c r="C3390" t="inlineStr">
         <is>
-          <t>FC St. Pauli</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="D3390" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>TSG Hoffenheim</t>
         </is>
       </c>
       <c r="E3390" t="inlineStr"/>
       <c r="F3390" t="inlineStr"/>
       <c r="G3390" t="n">
-        <v>6188</v>
+        <v>6187</v>
       </c>
     </row>
     <row r="3391">
       <c r="A3391" t="inlineStr">
         <is>
-          <t>2b9ab502221f28a483bd6e15c912aa8a</t>
+          <t>65d056ea3a51f7e6e81d67d53087f003</t>
         </is>
       </c>
       <c r="B3391" s="2" t="n">
@@ -87913,149 +87909,161 @@
       </c>
       <c r="C3391" t="inlineStr">
         <is>
-          <t>1. FC Heidenheim</t>
+          <t>Borussia Monchengladbach</t>
         </is>
       </c>
       <c r="D3391" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="E3391" t="inlineStr"/>
       <c r="F3391" t="inlineStr"/>
       <c r="G3391" t="n">
-        <v>6184</v>
+        <v>6189</v>
       </c>
     </row>
     <row r="3392">
       <c r="A3392" t="inlineStr">
         <is>
-          <t>45c1a5890b03f21bc137340dabc4a7d3</t>
+          <t>cb1545f23891ab4cd7f639221a0a152f</t>
         </is>
       </c>
       <c r="B3392" s="2" t="n">
-        <v>45892.5625</v>
+        <v>45893.625</v>
       </c>
       <c r="C3392" t="inlineStr">
         <is>
-          <t>SC Freiburg</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D3392" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="E3392" t="inlineStr"/>
       <c r="F3392" t="inlineStr"/>
       <c r="G3392" t="n">
-        <v>6186</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="3393">
       <c r="A3393" t="inlineStr">
         <is>
-          <t>5b2fff8ea253f0c94af5756895b7f149</t>
+          <t>3585107a897d05342af0596325ea0a35</t>
         </is>
       </c>
       <c r="B3393" s="2" t="n">
-        <v>45892.5625</v>
+        <v>45893.625</v>
       </c>
       <c r="C3393" t="inlineStr">
         <is>
-          <t>FSV Mainz 05</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D3393" t="inlineStr">
         <is>
-          <t>1. FC Köln</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="E3393" t="inlineStr"/>
       <c r="F3393" t="inlineStr"/>
       <c r="G3393" t="n">
-        <v>6185</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="3394">
       <c r="A3394" t="inlineStr">
         <is>
-          <t>a81fc1a653444c18ddbfa894d842571c</t>
+          <t>4f4ab56e4910a957e9d9c01d36477739</t>
         </is>
       </c>
       <c r="B3394" s="2" t="n">
-        <v>45892.5625</v>
+        <v>45893.625</v>
       </c>
       <c r="C3394" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D3394" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="E3394" t="inlineStr"/>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="E3394" t="inlineStr">
+        <is>
+          <t>(7a658ea87b4d915ed844b28da7d2993c,2025-08-23T16:30:00Z)</t>
+        </is>
+      </c>
       <c r="F3394" t="inlineStr"/>
       <c r="G3394" t="n">
-        <v>6190</v>
+        <v>8410</v>
       </c>
     </row>
     <row r="3395">
       <c r="A3395" t="inlineStr">
         <is>
-          <t>4b5bf052ddefb56d61c95922406bfa13</t>
+          <t>b60897d4cbdc07855a46a1bb520d78bb</t>
         </is>
       </c>
       <c r="B3395" s="2" t="n">
-        <v>45892.5625</v>
+        <v>45893.625</v>
       </c>
       <c r="C3395" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D3395" t="inlineStr">
         <is>
-          <t>TSG Hoffenheim</t>
-        </is>
-      </c>
-      <c r="E3395" t="inlineStr"/>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="E3395" t="inlineStr">
+        <is>
+          <t>(4efa457bb478d27dd6d65f1e995bf5ae,2025-08-23T16:30:00Z)</t>
+        </is>
+      </c>
       <c r="F3395" t="inlineStr"/>
       <c r="G3395" t="n">
-        <v>6187</v>
+        <v>8411</v>
       </c>
     </row>
     <row r="3396">
       <c r="A3396" t="inlineStr">
         <is>
-          <t>65d056ea3a51f7e6e81d67d53087f003</t>
+          <t>6f77d356b8d69db92c7d8bb4eef01f5c</t>
         </is>
       </c>
       <c r="B3396" s="2" t="n">
-        <v>45892.5625</v>
+        <v>45893.625</v>
       </c>
       <c r="C3396" t="inlineStr">
         <is>
-          <t>Borussia Monchengladbach</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="D3396" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
-        </is>
-      </c>
-      <c r="E3396" t="inlineStr"/>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="E3396" t="inlineStr">
+        <is>
+          <t>(5717a8bfc9f21ea6787da9293ecdb4ad,2025-08-23T18:45:00Z)</t>
+        </is>
+      </c>
       <c r="F3396" t="inlineStr"/>
       <c r="G3396" t="n">
-        <v>6189</v>
+        <v>8412</v>
       </c>
     </row>
     <row r="3397">
       <c r="A3397" t="inlineStr">
         <is>
-          <t>cb1545f23891ab4cd7f639221a0a152f</t>
+          <t>496e3fceabaae6029c0a23ff5520fb1c</t>
         </is>
       </c>
       <c r="B3397" s="2" t="n">
@@ -88063,24 +88071,28 @@
       </c>
       <c r="C3397" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="D3397" t="inlineStr">
         <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="E3397" t="inlineStr"/>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="E3397" t="inlineStr">
+        <is>
+          <t>(7b9513d902d1a775fcf02ed14d3ecf2f,2025-08-23T18:45:00Z)</t>
+        </is>
+      </c>
       <c r="F3397" t="inlineStr"/>
       <c r="G3397" t="n">
-        <v>1751</v>
+        <v>8413</v>
       </c>
     </row>
     <row r="3398">
       <c r="A3398" t="inlineStr">
         <is>
-          <t>3585107a897d05342af0596325ea0a35</t>
+          <t>a6d06a886371a723b6dd04a541b360fb</t>
         </is>
       </c>
       <c r="B3398" s="2" t="n">
@@ -88088,24 +88100,24 @@
       </c>
       <c r="C3398" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Atalanta BC</t>
         </is>
       </c>
       <c r="D3398" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="E3398" t="inlineStr"/>
       <c r="F3398" t="inlineStr"/>
       <c r="G3398" t="n">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="3399">
       <c r="A3399" t="inlineStr">
         <is>
-          <t>4f4ab56e4910a957e9d9c01d36477739</t>
+          <t>3ed3ecdae784a95f5078851a8a211a39</t>
         </is>
       </c>
       <c r="B3399" s="2" t="n">
@@ -88113,216 +88125,75 @@
       </c>
       <c r="C3399" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D3399" t="inlineStr">
         <is>
-          <t>Lecce</t>
-        </is>
-      </c>
-      <c r="E3399" t="inlineStr">
-        <is>
-          <t>(7a658ea87b4d915ed844b28da7d2993c,2025-08-23T16:30:00Z)</t>
-        </is>
-      </c>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="E3399" t="inlineStr"/>
       <c r="F3399" t="inlineStr"/>
       <c r="G3399" t="n">
-        <v>8410</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="3400">
       <c r="A3400" t="inlineStr">
         <is>
-          <t>b60897d4cbdc07855a46a1bb520d78bb</t>
+          <t>f78d4e5a5101834625585fc6d1376c89</t>
         </is>
       </c>
       <c r="B3400" s="2" t="n">
-        <v>45893.625</v>
+        <v>45894.6875</v>
       </c>
       <c r="C3400" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D3400" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="E3400" t="inlineStr">
         <is>
-          <t>(4efa457bb478d27dd6d65f1e995bf5ae,2025-08-23T16:30:00Z)</t>
+          <t>(1681112efa60161d64e5f6d748830a56,2025-08-24T15:00:00Z)</t>
         </is>
       </c>
       <c r="F3400" t="inlineStr"/>
       <c r="G3400" t="n">
-        <v>8411</v>
+        <v>8408</v>
       </c>
     </row>
     <row r="3401">
       <c r="A3401" t="inlineStr">
         <is>
-          <t>6f77d356b8d69db92c7d8bb4eef01f5c</t>
+          <t>f6050ded85182a39727a1ca894fed887</t>
         </is>
       </c>
       <c r="B3401" s="2" t="n">
-        <v>45893.625</v>
+        <v>45894.78125</v>
       </c>
       <c r="C3401" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="D3401" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="E3401" t="inlineStr">
         <is>
-          <t>(5717a8bfc9f21ea6787da9293ecdb4ad,2025-08-23T18:45:00Z)</t>
+          <t>(1453ca4ee62264f59d9f3181d10ac8ad,2025-08-24T15:00:00Z)</t>
         </is>
       </c>
       <c r="F3401" t="inlineStr"/>
       <c r="G3401" t="n">
-        <v>8412</v>
-      </c>
-    </row>
-    <row r="3402">
-      <c r="A3402" t="inlineStr">
-        <is>
-          <t>496e3fceabaae6029c0a23ff5520fb1c</t>
-        </is>
-      </c>
-      <c r="B3402" s="2" t="n">
-        <v>45893.625</v>
-      </c>
-      <c r="C3402" t="inlineStr">
-        <is>
-          <t>AS Roma</t>
-        </is>
-      </c>
-      <c r="D3402" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
-      <c r="E3402" t="inlineStr">
-        <is>
-          <t>(7b9513d902d1a775fcf02ed14d3ecf2f,2025-08-23T18:45:00Z)</t>
-        </is>
-      </c>
-      <c r="F3402" t="inlineStr"/>
-      <c r="G3402" t="n">
-        <v>8413</v>
-      </c>
-    </row>
-    <row r="3403">
-      <c r="A3403" t="inlineStr">
-        <is>
-          <t>a6d06a886371a723b6dd04a541b360fb</t>
-        </is>
-      </c>
-      <c r="B3403" s="2" t="n">
-        <v>45893.625</v>
-      </c>
-      <c r="C3403" t="inlineStr">
-        <is>
-          <t>Atalanta BC</t>
-        </is>
-      </c>
-      <c r="D3403" t="inlineStr">
-        <is>
-          <t>Pisa</t>
-        </is>
-      </c>
-      <c r="E3403" t="inlineStr"/>
-      <c r="F3403" t="inlineStr"/>
-      <c r="G3403" t="n">
-        <v>1749</v>
-      </c>
-    </row>
-    <row r="3404">
-      <c r="A3404" t="inlineStr">
-        <is>
-          <t>3ed3ecdae784a95f5078851a8a211a39</t>
-        </is>
-      </c>
-      <c r="B3404" s="2" t="n">
-        <v>45893.625</v>
-      </c>
-      <c r="C3404" t="inlineStr">
-        <is>
-          <t>Juventus</t>
-        </is>
-      </c>
-      <c r="D3404" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="E3404" t="inlineStr"/>
-      <c r="F3404" t="inlineStr"/>
-      <c r="G3404" t="n">
-        <v>1752</v>
-      </c>
-    </row>
-    <row r="3405">
-      <c r="A3405" t="inlineStr">
-        <is>
-          <t>f78d4e5a5101834625585fc6d1376c89</t>
-        </is>
-      </c>
-      <c r="B3405" s="2" t="n">
-        <v>45894.6875</v>
-      </c>
-      <c r="C3405" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="D3405" t="inlineStr">
-        <is>
-          <t>Hellas Verona</t>
-        </is>
-      </c>
-      <c r="E3405" t="inlineStr">
-        <is>
-          <t>(1681112efa60161d64e5f6d748830a56,2025-08-24T15:00:00Z)</t>
-        </is>
-      </c>
-      <c r="F3405" t="inlineStr"/>
-      <c r="G3405" t="n">
-        <v>8408</v>
-      </c>
-    </row>
-    <row r="3406">
-      <c r="A3406" t="inlineStr">
-        <is>
-          <t>f6050ded85182a39727a1ca894fed887</t>
-        </is>
-      </c>
-      <c r="B3406" s="2" t="n">
-        <v>45894.78125</v>
-      </c>
-      <c r="C3406" t="inlineStr">
-        <is>
-          <t>Inter Milan</t>
-        </is>
-      </c>
-      <c r="D3406" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="E3406" t="inlineStr">
-        <is>
-          <t>(1453ca4ee62264f59d9f3181d10ac8ad,2025-08-24T15:00:00Z)</t>
-        </is>
-      </c>
-      <c r="F3406" t="inlineStr"/>
-      <c r="G3406" t="n">
         <v>8409</v>
       </c>
     </row>
